--- a/deliverables/deliverables-20260120-0030/Model_4_Transmission.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_4_Transmission.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,10 +19,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.0_);(#,##0.0)"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,6 +52,21 @@
     <font>
       <b val="1"/>
       <color rgb="000000FF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -103,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -116,17 +132,25 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -201,6 +225,206 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Lotus Infrastructure</author>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0" shapeId="0">
+      <text>
+        <t>Exit value = RAB × multiple, not EBITDA × multiple. RAB grows with capex, shrinks with depreciation.</t>
+      </text>
+    </comment>
+    <comment ref="C4" authorId="0" shapeId="0">
+      <text>
+        <t>Earnings Before Interest, Taxes, Depreciation, Amortization. Cash earnings available to service debt and pay equity.</t>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0">
+      <text>
+        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal. DSCR = CFADS ÷ DS.</t>
+      </text>
+    </comment>
+    <comment ref="C6" authorId="0" shapeId="0">
+      <text>
+        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+      </text>
+    </comment>
+    <comment ref="C7" authorId="0" shapeId="0">
+      <text>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+      </text>
+    </comment>
+    <comment ref="C8" authorId="0" shapeId="0">
+      <text>
+        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money. Less sensitive to timing than IRR.</t>
+      </text>
+    </comment>
+    <comment ref="C9" authorId="0" shapeId="0">
+      <text>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+      </text>
+    </comment>
+    <comment ref="C13" authorId="0" shapeId="0">
+      <text>
+        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+      </text>
+    </comment>
+    <comment ref="C23" authorId="0" shapeId="0">
+      <text>
+        <t>Maximum power that can flow through line. Determines tariff revenue base.</t>
+      </text>
+    </comment>
+    <comment ref="C24" authorId="0" shapeId="0">
+      <text>
+        <t>Transmission availability typically 97-99%. Revenue tied to availability, not actual flow.</t>
+      </text>
+    </comment>
+    <comment ref="C28" authorId="0" shapeId="0">
+      <text>
+        <t>Regulated return on RAB. Predictable but subject to regulatory reset risk. Often inflation-linked.</t>
+      </text>
+    </comment>
+    <comment ref="C29" authorId="0" shapeId="0">
+      <text>
+        <t>Regulated return on RAB. Predictable but subject to regulatory reset risk. Often inflation-linked.</t>
+      </text>
+    </comment>
+    <comment ref="C37" authorId="0" shapeId="0">
+      <text>
+        <t>Exit value = RAB × multiple, not EBITDA × multiple. RAB grows with capex, shrinks with depreciation.</t>
+      </text>
+    </comment>
+    <comment ref="C38" authorId="0" shapeId="0">
+      <text>
+        <t>Includes spread over benchmark (SOFR). Investment grade infra: 150-250 bps spread. Sub-IG: 300-500 bps.</t>
+      </text>
+    </comment>
+    <comment ref="C39" authorId="0" shapeId="0">
+      <text>
+        <t>6 months is market standard. Provides lender runway if borrower misses payment. Funded at close.</t>
+      </text>
+    </comment>
+    <comment ref="C40" authorId="0" shapeId="0">
+      <text>
+        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+      </text>
+    </comment>
+    <comment ref="C41" authorId="0" shapeId="0">
+      <text>
+        <t>If DSCR falls below this level, cash is trapped and cannot be distributed to equity. Typically 1.10-1.15x.</t>
+      </text>
+    </comment>
+    <comment ref="C44" authorId="0" shapeId="0">
+      <text>
+        <t>Exit value = RAB × multiple, not EBITDA × multiple. RAB grows with capex, shrinks with depreciation.</t>
+      </text>
+    </comment>
+    <comment ref="C45" authorId="0" shapeId="0">
+      <text>
+        <t>Typical PE hold is 5-7 years. Often aligned with debt tenor to avoid refinancing risk.</t>
+      </text>
+    </comment>
+    <comment ref="C48" authorId="0" shapeId="0">
+      <text>
+        <t>US federal ~21% + state. Use blended effective rate. Shields reduce taxable income.</t>
+      </text>
+    </comment>
+    <comment ref="C52" authorId="0" shapeId="0">
+      <text>
+        <t>Interest accrues on outstanding balance. As principal amortizes, interest drops — the deleveraging benefit to equity.</t>
+      </text>
+    </comment>
+    <comment ref="C53" authorId="0" shapeId="0">
+      <text>
+        <t>Exit value = RAB × multiple, not EBITDA × multiple. RAB grows with capex, shrinks with depreciation.</t>
+      </text>
+    </comment>
+    <comment ref="C65" authorId="0" shapeId="0">
+      <text>
+        <t>Regulated return on RAB. Predictable but subject to regulatory reset risk. Often inflation-linked.</t>
+      </text>
+    </comment>
+    <comment ref="C70" authorId="0" shapeId="0">
+      <text>
+        <t>Earnings Before Interest, Taxes, Depreciation, Amortization. Cash earnings available to service debt and pay equity.</t>
+      </text>
+    </comment>
+    <comment ref="C76" authorId="0" shapeId="0">
+      <text>
+        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal. DSCR = CFADS ÷ DS.</t>
+      </text>
+    </comment>
+    <comment ref="C79" authorId="0" shapeId="0">
+      <text>
+        <t>Debt outstanding at start of year. Decreases as principal is paid or swept.</t>
+      </text>
+    </comment>
+    <comment ref="C80" authorId="0" shapeId="0">
+      <text>
+        <t>Interest accrues on outstanding balance. As principal amortizes, interest drops — the deleveraging benefit to equity.</t>
+      </text>
+    </comment>
+    <comment ref="C84" authorId="0" shapeId="0">
+      <text>
+        <t>Debt remaining after payments. Should reach zero by tenor end. MAX(0,...) prevents negative balance.</t>
+      </text>
+    </comment>
+    <comment ref="C85" authorId="0" shapeId="0">
+      <text>
+        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+      </text>
+    </comment>
+    <comment ref="C88" authorId="0" shapeId="0">
+      <text>
+        <t>Reserve sized to cover NEXT years debt service. Uses SCHEDULED DS (not actual) to avoid circular reference. Released at exit.</t>
+      </text>
+    </comment>
+    <comment ref="C90" authorId="0" shapeId="0">
+      <text>
+        <t>Positive = funding requirement (reduces distributable). Negative = release (increases distributable).</t>
+      </text>
+    </comment>
+    <comment ref="C96" authorId="0" shapeId="0">
+      <text>
+        <t>Cash available to equity after debt service and DSRA. Trapped if DSCR below lock-up threshold.</t>
+      </text>
+    </comment>
+    <comment ref="C103" authorId="0" shapeId="0">
+      <text>
+        <t>Interest accrues on outstanding balance. As principal amortizes, interest drops — the deleveraging benefit to equity.</t>
+      </text>
+    </comment>
+    <comment ref="C104" authorId="0" shapeId="0">
+      <text>
+        <t>Positive = funding requirement (reduces distributable). Negative = release (increases distributable).</t>
+      </text>
+    </comment>
+    <comment ref="C116" authorId="0" shapeId="0">
+      <text>
+        <t>Exit value = RAB × multiple, not EBITDA × multiple. RAB grows with capex, shrinks with depreciation.</t>
+      </text>
+    </comment>
+    <comment ref="C124" authorId="0" shapeId="0">
+      <text>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+      </text>
+    </comment>
+    <comment ref="C125" authorId="0" shapeId="0">
+      <text>
+        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money. Less sensitive to timing than IRR.</t>
+      </text>
+    </comment>
+    <comment ref="C129" authorId="0" shapeId="0">
+      <text>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -582,7 +806,11 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr"/>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Regulated Asset Base</t>
+        </is>
+      </c>
       <c r="D3" s="7">
         <f>$D$53</f>
         <v/>
@@ -599,7 +827,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr"/>
+      <c r="C4" s="6">
+        <f> Revenue − OpEx</f>
+        <v/>
+      </c>
       <c r="D4" s="7">
         <f>G70</f>
         <v/>
@@ -616,7 +847,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr"/>
+      <c r="C5" s="6">
+        <f> EBITDA − Taxes</f>
+        <v/>
+      </c>
       <c r="D5" s="7">
         <f>AVERAGE(G76:N76)</f>
         <v/>
@@ -633,8 +867,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="8">
+      <c r="C6" s="6">
+        <f> CFADS / Debt Service</f>
+        <v/>
+      </c>
+      <c r="D6" s="19">
         <f>MIN(G85:N85)</f>
         <v/>
       </c>
@@ -650,8 +887,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="9">
+      <c r="C7" s="6">
+        <f> IRR(Equity CF)</f>
+        <v/>
+      </c>
+      <c r="D7" s="20">
         <f>D124</f>
         <v/>
       </c>
@@ -667,8 +907,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="8">
+      <c r="C8" s="6">
+        <f> Total In / Total Out</f>
+        <v/>
+      </c>
+      <c r="D8" s="19">
         <f>D125</f>
         <v/>
       </c>
@@ -684,8 +927,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="9">
+      <c r="C9" s="6">
+        <f> IRR(Equity CF)</f>
+        <v/>
+      </c>
+      <c r="D9" s="20">
         <f>D129</f>
         <v/>
       </c>
@@ -743,7 +989,10 @@
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr"/>
-      <c r="C13" s="6" t="inlineStr"/>
+      <c r="C13" s="6">
+        <f> CFADS / Debt Service</f>
+        <v/>
+      </c>
       <c r="D13" s="10">
         <f>IF(D6&gt;=1.35,"PASS","FAIL")</f>
         <v/>
@@ -905,7 +1154,7 @@
           <t>Expected uptime</t>
         </is>
       </c>
-      <c r="D24" s="13" t="n">
+      <c r="D24" s="21" t="n">
         <v>0.98</v>
       </c>
     </row>
@@ -985,7 +1234,7 @@
           <t>Rate increase</t>
         </is>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="21" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -1045,7 +1294,7 @@
           <t>Cost escalation</t>
         </is>
       </c>
-      <c r="D33" s="13" t="n">
+      <c r="D33" s="21" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -1085,7 +1334,7 @@
           <t>Const loan leverage</t>
         </is>
       </c>
-      <c r="D36" s="13" t="n">
+      <c r="D36" s="21" t="n">
         <v>0.85</v>
       </c>
     </row>
@@ -1105,7 +1354,7 @@
           <t>Refi at COD</t>
         </is>
       </c>
-      <c r="D37" s="13" t="n">
+      <c r="D37" s="21" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -1125,7 +1374,7 @@
           <t>All-in rate</t>
         </is>
       </c>
-      <c r="D38" s="13" t="n">
+      <c r="D38" s="21" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -1165,7 +1414,7 @@
           <t>For sculpting</t>
         </is>
       </c>
-      <c r="D40" s="14" t="n">
+      <c r="D40" s="22" t="n">
         <v>1.4</v>
       </c>
     </row>
@@ -1185,7 +1434,7 @@
           <t>Distribution threshold</t>
         </is>
       </c>
-      <c r="D41" s="14" t="n">
+      <c r="D41" s="22" t="n">
         <v>1.15</v>
       </c>
     </row>
@@ -1225,7 +1474,7 @@
           <t>Exit at RAB multiple</t>
         </is>
       </c>
-      <c r="D44" s="14" t="n">
+      <c r="D44" s="22" t="n">
         <v>1.15</v>
       </c>
     </row>
@@ -1285,7 +1534,7 @@
           <t>Blended federal + state</t>
         </is>
       </c>
-      <c r="D48" s="13" t="n">
+      <c r="D48" s="21" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -1560,7 +1809,7 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Escalated</t>
+          <t>$/kW-yr regulated rate</t>
         </is>
       </c>
       <c r="E65" s="15">
@@ -1729,7 +1978,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C70" s="6" t="inlineStr"/>
+      <c r="C70" s="6">
+        <f> Revenue − OpEx</f>
+        <v/>
+      </c>
       <c r="E70" s="7">
         <f>E67-E68</f>
         <v/>
@@ -2050,7 +2302,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr"/>
+      <c r="C79" s="6">
+        <f> Prior Yr End Bal</f>
+        <v/>
+      </c>
       <c r="E79" s="15">
         <f>0</f>
         <v/>
@@ -2393,43 +2648,43 @@
           <t>CFADS / Actual DS</t>
         </is>
       </c>
-      <c r="E85" s="8">
+      <c r="E85" s="19">
         <f>IF(E83&gt;0,E76/E83,0)</f>
         <v/>
       </c>
-      <c r="F85" s="8">
+      <c r="F85" s="19">
         <f>IF(F83&gt;0,F76/F83,0)</f>
         <v/>
       </c>
-      <c r="G85" s="8">
+      <c r="G85" s="19">
         <f>IF(G83&gt;0,G76/G83,0)</f>
         <v/>
       </c>
-      <c r="H85" s="8">
+      <c r="H85" s="19">
         <f>IF(H83&gt;0,H76/H83,0)</f>
         <v/>
       </c>
-      <c r="I85" s="8">
+      <c r="I85" s="19">
         <f>IF(I83&gt;0,I76/I83,0)</f>
         <v/>
       </c>
-      <c r="J85" s="8">
+      <c r="J85" s="19">
         <f>IF(J83&gt;0,J76/J83,0)</f>
         <v/>
       </c>
-      <c r="K85" s="8">
+      <c r="K85" s="19">
         <f>IF(K83&gt;0,K76/K83,0)</f>
         <v/>
       </c>
-      <c r="L85" s="8">
+      <c r="L85" s="19">
         <f>IF(L83&gt;0,L76/L83,0)</f>
         <v/>
       </c>
-      <c r="M85" s="8">
+      <c r="M85" s="19">
         <f>IF(M83&gt;0,M76/M83,0)</f>
         <v/>
       </c>
-      <c r="N85" s="8">
+      <c r="N85" s="19">
         <f>IF(N83&gt;0,N76/N83,0)</f>
         <v/>
       </c>
@@ -2972,7 +3227,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C103" s="6" t="inlineStr"/>
+      <c r="C103" s="6">
+        <f> Beg Bal × Rate</f>
+        <v/>
+      </c>
       <c r="D103" s="15">
         <f>$D$52</f>
         <v/>
@@ -2989,7 +3247,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C104" s="6" t="inlineStr"/>
+      <c r="C104" s="6">
+        <f> Target − Beginning</f>
+        <v/>
+      </c>
       <c r="D104" s="15">
         <f>G88</f>
         <v/>
@@ -3336,8 +3597,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C124" s="6" t="inlineStr"/>
-      <c r="D124" s="9">
+      <c r="C124" s="6">
+        <f> IRR(Equity CF)</f>
+        <v/>
+      </c>
+      <c r="D124" s="20">
         <f>IRR(D123:N123)</f>
         <v/>
       </c>
@@ -3358,7 +3622,7 @@
           <t>Sum inflows / outflows</t>
         </is>
       </c>
-      <c r="D125" s="8">
+      <c r="D125" s="19">
         <f>SUMIF(D123:N123,"&gt;0")/-SUMIF(D123:N123,"&lt;0")</f>
         <v/>
       </c>
@@ -3440,10 +3704,204 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C129" s="6" t="inlineStr"/>
-      <c r="D129" s="9">
+      <c r="C129" s="6">
+        <f> IRR(Equity CF)</f>
+        <v/>
+      </c>
+      <c r="D129" s="20">
         <f>IRR(D128:N128)</f>
         <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="90" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>INVESTMENT COMMITTEE MEMORANDUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>High-Voltage Transmission Line</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>EXECUTIVE SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>• Develop 200-mile, 500 kV transmission line at $850mm total cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>• Regulated asset with 40-year tariff at $180/kW-yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>• 3-year construction, 37-year operating period</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>• Target returns: 9-11% levered IRR, 1.5-1.7x MOIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1"/>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>1. Regulated, predictable cash flows</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   FERC-approved tariff provides long-term revenue certainty. Inflation escalators protect real returns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>2. Essential infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Transmission is critical for renewable integration. Regulatory support for new build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>3. RAB-based exit valuation</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Exit at RAB multiple provides valuation floor independent of market conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1"/>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>KEY RISKS &amp; MITIGANTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>Risk | Mitigant</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>Construction execution | EPC contract with liquidated damages; experienced contractor</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>Regulatory reset risk | Long tariff term (40 yr); track record of fair treatment</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>Interest rate sensitivity | Fixed-rate debt; long tenor matches asset life</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1"/>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>FINANCIAL SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>Entry EV: $850mm | Leverage: 70% | Min DSCR: 1.40x</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>Levered IRR: 10.0% | MOIC: 1.6x</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1"/>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>RECOMMENDATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Recommend APPROVAL subject to satisfactory completion of confirmatory due diligence.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/deliverables/deliverables-20260120-0030/Model_4_Transmission.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_4_Transmission.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +21,7 @@
     <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,21 +51,6 @@
     <font>
       <b val="1"/>
       <color rgb="000000FF"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -119,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -147,10 +131,6 @@
     <xf numFmtId="166" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -233,194 +213,84 @@
     <author>Lotus Infrastructure</author>
   </authors>
   <commentList>
-    <comment ref="C3" authorId="0" shapeId="0">
-      <text>
-        <t>Exit value = RAB × multiple, not EBITDA × multiple. RAB grows with capex, shrinks with depreciation.</t>
-      </text>
-    </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>Earnings Before Interest, Taxes, Depreciation, Amortization. Cash earnings available to service debt and pay equity.</t>
+        <t>Cash earnings before financing. What is available to service debt and pay equity.</t>
       </text>
     </comment>
     <comment ref="C5" authorId="0" shapeId="0">
       <text>
-        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal. DSCR = CFADS ÷ DS.</t>
+        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal.</t>
       </text>
     </comment>
     <comment ref="C6" authorId="0" shapeId="0">
       <text>
-        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+        <t>Debt Service Coverage Ratio. Key lender metric. Target: 1.25-1.40x.</t>
       </text>
     </comment>
     <comment ref="C7" authorId="0" shapeId="0">
       <text>
-        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra).</t>
       </text>
     </comment>
     <comment ref="C8" authorId="0" shapeId="0">
       <text>
-        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money. Less sensitive to timing than IRR.</t>
+        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money.</t>
       </text>
     </comment>
     <comment ref="C9" authorId="0" shapeId="0">
       <text>
-        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra).</t>
       </text>
     </comment>
     <comment ref="C13" authorId="0" shapeId="0">
       <text>
-        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
-      </text>
-    </comment>
-    <comment ref="C23" authorId="0" shapeId="0">
-      <text>
-        <t>Maximum power that can flow through line. Determines tariff revenue base.</t>
-      </text>
-    </comment>
-    <comment ref="C24" authorId="0" shapeId="0">
-      <text>
-        <t>Transmission availability typically 97-99%. Revenue tied to availability, not actual flow.</t>
-      </text>
-    </comment>
-    <comment ref="C28" authorId="0" shapeId="0">
-      <text>
-        <t>Regulated return on RAB. Predictable but subject to regulatory reset risk. Often inflation-linked.</t>
-      </text>
-    </comment>
-    <comment ref="C29" authorId="0" shapeId="0">
-      <text>
-        <t>Regulated return on RAB. Predictable but subject to regulatory reset risk. Often inflation-linked.</t>
-      </text>
-    </comment>
-    <comment ref="C37" authorId="0" shapeId="0">
-      <text>
-        <t>Exit value = RAB × multiple, not EBITDA × multiple. RAB grows with capex, shrinks with depreciation.</t>
-      </text>
-    </comment>
-    <comment ref="C38" authorId="0" shapeId="0">
-      <text>
-        <t>Includes spread over benchmark (SOFR). Investment grade infra: 150-250 bps spread. Sub-IG: 300-500 bps.</t>
-      </text>
-    </comment>
-    <comment ref="C39" authorId="0" shapeId="0">
-      <text>
-        <t>6 months is market standard. Provides lender runway if borrower misses payment. Funded at close.</t>
+        <t>Debt Service Coverage Ratio. Key lender metric. Target: 1.25-1.40x.</t>
       </text>
     </comment>
     <comment ref="C40" authorId="0" shapeId="0">
       <text>
-        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+        <t>Debt Service Coverage Ratio. Key lender metric. Target: 1.25-1.40x.</t>
       </text>
     </comment>
     <comment ref="C41" authorId="0" shapeId="0">
       <text>
-        <t>If DSCR falls below this level, cash is trapped and cannot be distributed to equity. Typically 1.10-1.15x.</t>
-      </text>
-    </comment>
-    <comment ref="C44" authorId="0" shapeId="0">
-      <text>
-        <t>Exit value = RAB × multiple, not EBITDA × multiple. RAB grows with capex, shrinks with depreciation.</t>
-      </text>
-    </comment>
-    <comment ref="C45" authorId="0" shapeId="0">
-      <text>
-        <t>Typical PE hold is 5-7 years. Often aligned with debt tenor to avoid refinancing risk.</t>
-      </text>
-    </comment>
-    <comment ref="C48" authorId="0" shapeId="0">
-      <text>
-        <t>US federal ~21% + state. Use blended effective rate. Shields reduce taxable income.</t>
-      </text>
-    </comment>
-    <comment ref="C52" authorId="0" shapeId="0">
-      <text>
-        <t>Interest accrues on outstanding balance. As principal amortizes, interest drops — the deleveraging benefit to equity.</t>
-      </text>
-    </comment>
-    <comment ref="C53" authorId="0" shapeId="0">
-      <text>
-        <t>Exit value = RAB × multiple, not EBITDA × multiple. RAB grows with capex, shrinks with depreciation.</t>
-      </text>
-    </comment>
-    <comment ref="C65" authorId="0" shapeId="0">
-      <text>
-        <t>Regulated return on RAB. Predictable but subject to regulatory reset risk. Often inflation-linked.</t>
+        <t>Debt Service Coverage Ratio. Key lender metric. Target: 1.25-1.40x.</t>
       </text>
     </comment>
     <comment ref="C70" authorId="0" shapeId="0">
       <text>
-        <t>Earnings Before Interest, Taxes, Depreciation, Amortization. Cash earnings available to service debt and pay equity.</t>
+        <t>Cash earnings before financing. What is available to service debt and pay equity.</t>
       </text>
     </comment>
     <comment ref="C76" authorId="0" shapeId="0">
       <text>
-        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal. DSCR = CFADS ÷ DS.</t>
-      </text>
-    </comment>
-    <comment ref="C79" authorId="0" shapeId="0">
-      <text>
-        <t>Debt outstanding at start of year. Decreases as principal is paid or swept.</t>
-      </text>
-    </comment>
-    <comment ref="C80" authorId="0" shapeId="0">
-      <text>
-        <t>Interest accrues on outstanding balance. As principal amortizes, interest drops — the deleveraging benefit to equity.</t>
-      </text>
-    </comment>
-    <comment ref="C84" authorId="0" shapeId="0">
-      <text>
-        <t>Debt remaining after payments. Should reach zero by tenor end. MAX(0,...) prevents negative balance.</t>
+        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal.</t>
       </text>
     </comment>
     <comment ref="C85" authorId="0" shapeId="0">
       <text>
-        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+        <t>Debt Service Coverage Ratio. Key lender metric. Target: 1.25-1.40x.</t>
       </text>
     </comment>
     <comment ref="C88" authorId="0" shapeId="0">
       <text>
-        <t>Reserve sized to cover NEXT years debt service. Uses SCHEDULED DS (not actual) to avoid circular reference. Released at exit.</t>
-      </text>
-    </comment>
-    <comment ref="C90" authorId="0" shapeId="0">
-      <text>
-        <t>Positive = funding requirement (reduces distributable). Negative = release (increases distributable).</t>
-      </text>
-    </comment>
-    <comment ref="C96" authorId="0" shapeId="0">
-      <text>
-        <t>Cash available to equity after debt service and DSRA. Trapped if DSCR below lock-up threshold.</t>
-      </text>
-    </comment>
-    <comment ref="C103" authorId="0" shapeId="0">
-      <text>
-        <t>Interest accrues on outstanding balance. As principal amortizes, interest drops — the deleveraging benefit to equity.</t>
-      </text>
-    </comment>
-    <comment ref="C104" authorId="0" shapeId="0">
-      <text>
-        <t>Positive = funding requirement (reduces distributable). Negative = release (increases distributable).</t>
-      </text>
-    </comment>
-    <comment ref="C116" authorId="0" shapeId="0">
-      <text>
-        <t>Exit value = RAB × multiple, not EBITDA × multiple. RAB grows with capex, shrinks with depreciation.</t>
+        <t>Reserve sized to cover NEXT years debt service. Uses SCHEDULED DS to avoid circular reference.</t>
       </text>
     </comment>
     <comment ref="C124" authorId="0" shapeId="0">
       <text>
-        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra).</t>
       </text>
     </comment>
     <comment ref="C125" authorId="0" shapeId="0">
       <text>
-        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money. Less sensitive to timing than IRR.</t>
+        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money.</t>
       </text>
     </comment>
     <comment ref="C129" authorId="0" shapeId="0">
       <text>
-        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra).</t>
       </text>
     </comment>
   </commentList>
@@ -716,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N129"/>
+  <dimension ref="A1:N159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -806,11 +676,7 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Regulated Asset Base</t>
-        </is>
-      </c>
+      <c r="C3" s="6" t="inlineStr"/>
       <c r="D3" s="7">
         <f>$D$53</f>
         <v/>
@@ -827,9 +693,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C4" s="6">
-        <f> Revenue − OpEx</f>
-        <v/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Revenue minus OpEx</t>
+        </is>
       </c>
       <c r="D4" s="7">
         <f>G70</f>
@@ -847,9 +714,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C5" s="6">
-        <f> EBITDA − Taxes</f>
-        <v/>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>EBITDA minus Taxes</t>
+        </is>
       </c>
       <c r="D5" s="7">
         <f>AVERAGE(G76:N76)</f>
@@ -867,9 +735,10 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C6" s="6">
-        <f> CFADS / Debt Service</f>
-        <v/>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>CFADS / Debt Service</t>
+        </is>
       </c>
       <c r="D6" s="19">
         <f>MIN(G85:N85)</f>
@@ -887,9 +756,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C7" s="6">
-        <f> IRR(Equity CF)</f>
-        <v/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
       </c>
       <c r="D7" s="20">
         <f>D124</f>
@@ -907,9 +777,10 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C8" s="6">
-        <f> Total In / Total Out</f>
-        <v/>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Total In / Total Out</t>
+        </is>
       </c>
       <c r="D8" s="19">
         <f>D125</f>
@@ -927,9 +798,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C9" s="6">
-        <f> IRR(Equity CF)</f>
-        <v/>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
       </c>
       <c r="D9" s="20">
         <f>D129</f>
@@ -989,15 +861,18 @@
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr"/>
-      <c r="C13" s="6">
-        <f> CFADS / Debt Service</f>
-        <v/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>CFADS / Debt Service</t>
+        </is>
       </c>
       <c r="D13" s="10">
         <f>IF(D6&gt;=1.35,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
+    <row r="14"/>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
@@ -1098,6 +973,7 @@
         <v>3</v>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
@@ -1178,6 +1054,7 @@
         <v>40</v>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
@@ -1238,6 +1115,7 @@
         <v>0.02</v>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
@@ -1298,6 +1176,7 @@
         <v>0.025</v>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
@@ -1438,6 +1317,7 @@
         <v>1.15</v>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
@@ -1498,6 +1378,7 @@
         <v>10</v>
       </c>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
@@ -1538,6 +1419,7 @@
         <v>0.25</v>
       </c>
     </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
@@ -1663,6 +1545,7 @@
         <v/>
       </c>
     </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
@@ -1776,6 +1659,7 @@
         <v/>
       </c>
     </row>
+    <row r="63"/>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
@@ -1809,7 +1693,7 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>$/kW-yr regulated rate</t>
+          <t>Escalated</t>
         </is>
       </c>
       <c r="E65" s="15">
@@ -1853,6 +1737,7 @@
         <v/>
       </c>
     </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
@@ -1967,6 +1852,7 @@
         <v/>
       </c>
     </row>
+    <row r="69"/>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
@@ -1978,9 +1864,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C70" s="6">
-        <f> Revenue − OpEx</f>
-        <v/>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Revenue minus OpEx</t>
+        </is>
       </c>
       <c r="E70" s="7">
         <f>E67-E68</f>
@@ -2023,6 +1910,7 @@
         <v/>
       </c>
     </row>
+    <row r="71"/>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
@@ -2271,6 +2159,7 @@
         <v/>
       </c>
     </row>
+    <row r="77"/>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
@@ -2302,10 +2191,7 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C79" s="6">
-        <f> Prior Yr End Bal</f>
-        <v/>
-      </c>
+      <c r="C79" s="6" t="inlineStr"/>
       <c r="E79" s="15">
         <f>0</f>
         <v/>
@@ -2689,6 +2575,7 @@
         <v/>
       </c>
     </row>
+    <row r="86"/>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
@@ -2949,6 +2836,7 @@
         <v/>
       </c>
     </row>
+    <row r="92"/>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
@@ -3136,6 +3024,7 @@
         <v/>
       </c>
     </row>
+    <row r="97"/>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
@@ -3227,10 +3116,7 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C103" s="6">
-        <f> Beg Bal × Rate</f>
-        <v/>
-      </c>
+      <c r="C103" s="6" t="inlineStr"/>
       <c r="D103" s="15">
         <f>$D$52</f>
         <v/>
@@ -3247,10 +3133,7 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C104" s="6">
-        <f> Target − Beginning</f>
-        <v/>
-      </c>
+      <c r="C104" s="6" t="inlineStr"/>
       <c r="D104" s="15">
         <f>G88</f>
         <v/>
@@ -3273,6 +3156,7 @@
         <v/>
       </c>
     </row>
+    <row r="106"/>
     <row r="107">
       <c r="A107" s="18" t="inlineStr">
         <is>
@@ -3363,6 +3247,7 @@
         <v/>
       </c>
     </row>
+    <row r="113"/>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
@@ -3509,6 +3394,7 @@
         <v/>
       </c>
     </row>
+    <row r="121"/>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
@@ -3597,9 +3483,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C124" s="6">
-        <f> IRR(Equity CF)</f>
-        <v/>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
       </c>
       <c r="D124" s="20">
         <f>IRR(D123:N123)</f>
@@ -3627,6 +3514,7 @@
         <v/>
       </c>
     </row>
+    <row r="126"/>
     <row r="127">
       <c r="A127" s="18" t="inlineStr">
         <is>
@@ -3704,207 +3592,48 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C129" s="6">
-        <f> IRR(Equity CF)</f>
-        <v/>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
       </c>
       <c r="D129" s="20">
         <f>IRR(D128:N128)</f>
         <v/>
       </c>
     </row>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="90" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
-        <is>
-          <t>INVESTMENT COMMITTEE MEMORANDUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>High-Voltage Transmission Line</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="24" t="inlineStr">
-        <is>
-          <t>EXECUTIVE SUMMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
-        <is>
-          <t>• Develop 200-mile, 500 kV transmission line at $850mm total cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="25" t="inlineStr">
-        <is>
-          <t>• Regulated asset with 40-year tariff at $180/kW-yr</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="25" t="inlineStr">
-        <is>
-          <t>• 3-year construction, 37-year operating period</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="25" t="inlineStr">
-        <is>
-          <t>• Target returns: 9-11% levered IRR, 1.5-1.7x MOIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1"/>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
-        <is>
-          <t>INVESTMENT THESIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="26" t="inlineStr">
-        <is>
-          <t>1. Regulated, predictable cash flows</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   FERC-approved tariff provides long-term revenue certainty. Inflation escalators protect real returns.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
-        <is>
-          <t>2. Essential infrastructure</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Transmission is critical for renewable integration. Regulatory support for new build.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>3. RAB-based exit valuation</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Exit at RAB multiple provides valuation floor independent of market conditions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1"/>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="24" t="inlineStr">
-        <is>
-          <t>KEY RISKS &amp; MITIGANTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="26" t="inlineStr">
-        <is>
-          <t>Risk | Mitigant</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="25" t="inlineStr">
-        <is>
-          <t>Construction execution | EPC contract with liquidated damages; experienced contractor</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>Regulatory reset risk | Long tariff term (40 yr); track record of fair treatment</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="25" t="inlineStr">
-        <is>
-          <t>Interest rate sensitivity | Fixed-rate debt; long tenor matches asset life</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1"/>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="24" t="inlineStr">
-        <is>
-          <t>FINANCIAL SUMMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="25" t="inlineStr">
-        <is>
-          <t>Entry EV: $850mm | Leverage: 70% | Min DSCR: 1.40x</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="25" t="inlineStr">
-        <is>
-          <t>Levered IRR: 10.0% | MOIC: 1.6x</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1"/>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="24" t="inlineStr">
-        <is>
-          <t>RECOMMENDATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="25" t="inlineStr">
-        <is>
-          <t>Recommend APPROVAL subject to satisfactory completion of confirmatory due diligence.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/deliverables/deliverables-20260120-0030/Model_4_Transmission.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_4_Transmission.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
     <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,6 +52,25 @@
     <font>
       <b val="1"/>
       <color rgb="000000FF"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -103,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -131,6 +151,18 @@
     <xf numFmtId="166" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -586,7 +618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N159"/>
+  <dimension ref="A1:N129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -871,8 +903,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
@@ -973,7 +1003,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
@@ -1054,7 +1083,6 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
@@ -1115,7 +1143,6 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
@@ -1176,7 +1203,6 @@
         <v>0.025</v>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
@@ -1317,7 +1343,6 @@
         <v>1.15</v>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
@@ -1378,7 +1403,6 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
@@ -1419,7 +1443,6 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="49"/>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
@@ -1545,7 +1568,6 @@
         <v/>
       </c>
     </row>
-    <row r="56"/>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
@@ -1659,7 +1681,6 @@
         <v/>
       </c>
     </row>
-    <row r="63"/>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
@@ -1737,7 +1758,6 @@
         <v/>
       </c>
     </row>
-    <row r="66"/>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
@@ -1852,7 +1872,6 @@
         <v/>
       </c>
     </row>
-    <row r="69"/>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
@@ -1910,7 +1929,6 @@
         <v/>
       </c>
     </row>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
@@ -2159,7 +2177,6 @@
         <v/>
       </c>
     </row>
-    <row r="77"/>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
@@ -2575,7 +2592,6 @@
         <v/>
       </c>
     </row>
-    <row r="86"/>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
@@ -2836,7 +2852,6 @@
         <v/>
       </c>
     </row>
-    <row r="92"/>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
@@ -3024,7 +3039,6 @@
         <v/>
       </c>
     </row>
-    <row r="97"/>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
@@ -3156,7 +3170,6 @@
         <v/>
       </c>
     </row>
-    <row r="106"/>
     <row r="107">
       <c r="A107" s="18" t="inlineStr">
         <is>
@@ -3247,7 +3260,6 @@
         <v/>
       </c>
     </row>
-    <row r="113"/>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
@@ -3394,7 +3406,6 @@
         <v/>
       </c>
     </row>
-    <row r="121"/>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
@@ -3514,7 +3525,6 @@
         <v/>
       </c>
     </row>
-    <row r="126"/>
     <row r="127">
       <c r="A127" s="18" t="inlineStr">
         <is>
@@ -3602,38 +3612,262 @@
         <v/>
       </c>
     </row>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="120" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>PROJECT CORRIDOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>INVESTMENT COMMITTEE MEMORANDUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>3,200 MW HVDC Transmission Line – SPP to MISO</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>RECOMMENDATION: Proceed to development at $585mm total investment</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>KEY METRICS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>• FERC-approved tariff provides stable, regulated return on 40-year asset life</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>• Critical infrastructure connecting low-cost wind to high-demand load centers</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>• Construction interest capitalization into RAB improves economics</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>• Exit at 1.15x RAB to infrastructure yield vehicles seeking stable returns</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>KEY RISKS &amp; MITIGANTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>ANTICIPATED IC Q&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>Q: Why does transmission trade at premium to RAB?</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>A: Scarcity value – new transmission is hard to permit. 40+ year life with stable regulated returns. Critical infrastructure status. 1.15x is conservative vs recent deals at 1.25x+.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>Q: Walk me through construction financing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>A: Y0-Y1: Equity funds development ($35mm). Y2: Construction loan (85% × $550mm = $467.5mm) + equity funds construction. Y3 (COD): Refi into term debt (60% × RAB) + equity to repay construction loan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>Q: What if construction is delayed?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>A: Higher capitalized interest, later revenue start. 6-month delay = ~80bps IRR reduction. Mitigated by fixed-price EPC with liquidated damages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>Q: What's the regulatory risk?</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>A: FERC could reduce allowed ROE. Historically stable at 10-11%. Even at 9%, returns still exceed cost of capital due to 60% leverage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="23" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>Metric | Base Case | Downside | Upside</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>RAB at COD | $608mm | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>Total Equity | $265mm | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="26" t="inlineStr">
+        <is>
+          <t>Term Debt % RAB | 60% | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>Levered IRR | 14.5% | 12.2% | 16.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="26" t="inlineStr">
+        <is>
+          <t>MOIC | 2.05x | 1.85x | 2.25x</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t>Min DSCR (Y3-Y10) | 1.40x | 1.32x | 1.48x</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="26" t="inlineStr">
+        <is>
+          <t>Risk | Probability | Mitigant</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="26" t="inlineStr">
+        <is>
+          <t>Construction delay/overrun | Medium | Fixed-price EPC; liquidated damages; contingency budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="26" t="inlineStr">
+        <is>
+          <t>Regulatory ROE reduction | Low | FERC historically stable; bipartisan transmission support</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="26" t="inlineStr">
+        <is>
+          <t>Permitting challenges | Medium | Pre-approved route; tribal and environmental clearances secured</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="26" t="inlineStr">
+        <is>
+          <t>Counterparty default | Low | Utility offtakers are investment-grade; regulatory backstop</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/deliverables/deliverables-20260120-0030/Model_4_Transmission.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_4_Transmission.xlsx
@@ -7,8 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Prompt" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,7 @@
     <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,6 +73,9 @@
     <font>
       <name val="Consolas"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -123,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -163,6 +168,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -618,6 +624,420 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Transmission - INTUITION MAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="27" t="inlineStr">
+        <is>
+          <t>WHAT THIS MODEL DOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regulated transmission - FERC ROE on rate base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>KEY VALUE DRIVERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1. FERC ROE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2. Rate Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3. Construction Timing</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>DEBT STRUCTURE RATIONALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sculpted 1.40x - regulated returns.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CASE STUDY: Transmission ACQUISITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Time: 4 hours | Deliverables: Model + IC Memo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>SITUATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>150-mile 345kV line, $180mm equity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>KEY QUESTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1. What levered IRR at indicative price?</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2. Downside DSCR under stress?</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3. Key diligence items?</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4. Protections to negotiate?</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="120" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>PROJECT CORRIDOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>INVESTMENT COMMITTEE MEMORANDUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>3,200 MW HVDC Transmission Line – SPP to MISO</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>RECOMMENDATION: Proceed to development at $585mm total investment</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>KEY METRICS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>• FERC-approved tariff provides stable, regulated return on 40-year asset life</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>• Critical infrastructure connecting low-cost wind to high-demand load centers</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>• Construction interest capitalization into RAB improves economics</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>• Exit at 1.15x RAB to infrastructure yield vehicles seeking stable returns</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>KEY RISKS &amp; MITIGANTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>ANTICIPATED IC Q&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>Q: Why does transmission trade at premium to RAB?</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>A: Scarcity value – new transmission is hard to permit. 40+ year life with stable regulated returns. Critical infrastructure status. 1.15x is conservative vs recent deals at 1.25x+.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>Q: Walk me through construction financing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>A: Y0-Y1: Equity funds development ($35mm). Y2: Construction loan (85% × $550mm = $467.5mm) + equity funds construction. Y3 (COD): Refi into term debt (60% × RAB) + equity to repay construction loan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>Q: What if construction is delayed?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>A: Higher capitalized interest, later revenue start. 6-month delay = ~80bps IRR reduction. Mitigated by fixed-price EPC with liquidated damages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>Q: What's the regulatory risk?</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>A: FERC could reduce allowed ROE. Historically stable at 10-11%. Even at 9%, returns still exceed cost of capital due to 60% leverage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="23" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>Metric | Base Case | Downside | Upside</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>RAB at COD | $608mm | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>Total Equity | $265mm | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="26" t="inlineStr">
+        <is>
+          <t>Term Debt % RAB | 60% | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>Levered IRR | 14.5% | 12.2% | 16.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="26" t="inlineStr">
+        <is>
+          <t>MOIC | 2.05x | 1.85x | 2.25x</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t>Min DSCR (Y3-Y10) | 1.40x | 1.32x | 1.48x</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="26" t="inlineStr">
+        <is>
+          <t>Risk | Probability | Mitigant</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="26" t="inlineStr">
+        <is>
+          <t>Construction delay/overrun | Medium | Fixed-price EPC; liquidated damages; contingency budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="26" t="inlineStr">
+        <is>
+          <t>Regulatory ROE reduction | Low | FERC historically stable; bipartisan transmission support</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="26" t="inlineStr">
+        <is>
+          <t>Permitting challenges | Medium | Pre-approved route; tribal and environmental clearances secured</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="26" t="inlineStr">
+        <is>
+          <t>Counterparty default | Low | Utility offtakers are investment-grade; regulatory backstop</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -773,7 +1193,7 @@
         </is>
       </c>
       <c r="D6" s="19">
-        <f>MIN(G85:N85)</f>
+        <f>IF(COUNTIF(G85:N85,"&gt;0")&gt;0,MINIFS(G85:N85,G85:N85,"&gt;0"),0)</f>
         <v/>
       </c>
     </row>
@@ -3616,258 +4036,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="23" t="inlineStr">
-        <is>
-          <t>PROJECT CORRIDOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>INVESTMENT COMMITTEE MEMORANDUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="23" t="inlineStr">
-        <is>
-          <t>3,200 MW HVDC Transmission Line – SPP to MISO</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="25" t="inlineStr">
-        <is>
-          <t>RECOMMENDATION: Proceed to development at $585mm total investment</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="23" t="inlineStr">
-        <is>
-          <t>────────────────────────────────────────────────────────────</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="24" t="inlineStr">
-        <is>
-          <t>KEY METRICS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="24" t="inlineStr">
-        <is>
-          <t>INVESTMENT THESIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>• FERC-approved tariff provides stable, regulated return on 40-year asset life</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="23" t="inlineStr">
-        <is>
-          <t>• Critical infrastructure connecting low-cost wind to high-demand load centers</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="23" t="inlineStr">
-        <is>
-          <t>• Construction interest capitalization into RAB improves economics</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="23" t="inlineStr">
-        <is>
-          <t>• Exit at 1.15x RAB to infrastructure yield vehicles seeking stable returns</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>KEY RISKS &amp; MITIGANTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="24" t="inlineStr">
-        <is>
-          <t>ANTICIPATED IC Q&amp;A</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="24" t="inlineStr">
-        <is>
-          <t>Q: Why does transmission trade at premium to RAB?</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t>A: Scarcity value – new transmission is hard to permit. 40+ year life with stable regulated returns. Critical infrastructure status. 1.15x is conservative vs recent deals at 1.25x+.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="24" t="inlineStr">
-        <is>
-          <t>Q: Walk me through construction financing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="23" t="inlineStr">
-        <is>
-          <t>A: Y0-Y1: Equity funds development ($35mm). Y2: Construction loan (85% × $550mm = $467.5mm) + equity funds construction. Y3 (COD): Refi into term debt (60% × RAB) + equity to repay construction loan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="24" t="inlineStr">
-        <is>
-          <t>Q: What if construction is delayed?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="23" t="inlineStr">
-        <is>
-          <t>A: Higher capitalized interest, later revenue start. 6-month delay = ~80bps IRR reduction. Mitigated by fixed-price EPC with liquidated damages.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="24" t="inlineStr">
-        <is>
-          <t>Q: What's the regulatory risk?</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="23" t="inlineStr">
-        <is>
-          <t>A: FERC could reduce allowed ROE. Historically stable at 10-11%. Even at 9%, returns still exceed cost of capital due to 60% leverage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="23" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="26" t="inlineStr">
-        <is>
-          <t>Metric | Base Case | Downside | Upside</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="26" t="inlineStr">
-        <is>
-          <t>RAB at COD | $608mm | - | -</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="26" t="inlineStr">
-        <is>
-          <t>Total Equity | $265mm | - | -</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="26" t="inlineStr">
-        <is>
-          <t>Term Debt % RAB | 60% | - | -</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="26" t="inlineStr">
-        <is>
-          <t>Levered IRR | 14.5% | 12.2% | 16.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="26" t="inlineStr">
-        <is>
-          <t>MOIC | 2.05x | 1.85x | 2.25x</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="26" t="inlineStr">
-        <is>
-          <t>Min DSCR (Y3-Y10) | 1.40x | 1.32x | 1.48x</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="23" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="26" t="inlineStr">
-        <is>
-          <t>Risk | Probability | Mitigant</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="26" t="inlineStr">
-        <is>
-          <t>Construction delay/overrun | Medium | Fixed-price EPC; liquidated damages; contingency budget</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="26" t="inlineStr">
-        <is>
-          <t>Regulatory ROE reduction | Low | FERC historically stable; bipartisan transmission support</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="26" t="inlineStr">
-        <is>
-          <t>Permitting challenges | Medium | Pre-approved route; tribal and environmental clearances secured</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="26" t="inlineStr">
-        <is>
-          <t>Counterparty default | Low | Utility offtakers are investment-grade; regulatory backstop</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/deliverables/deliverables-20260120-0030/Model_4_Transmission.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_4_Transmission.xlsx
@@ -3459,6 +3459,7 @@
         <v/>
       </c>
     </row>
+    <row r="97"/>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
@@ -3590,6 +3591,7 @@
         <v/>
       </c>
     </row>
+    <row r="106"/>
     <row r="107">
       <c r="A107" s="18" t="inlineStr">
         <is>
@@ -3663,7 +3665,7 @@
       </c>
       <c r="C111" s="6" t="inlineStr"/>
       <c r="D111" s="7">
-        <f>D109+D110+D104</f>
+        <f>D109+D110</f>
         <v/>
       </c>
     </row>
@@ -3676,10 +3678,11 @@
       <c r="B112" s="6" t="inlineStr"/>
       <c r="C112" s="6" t="inlineStr"/>
       <c r="D112" s="10">
-        <f>IF(ABS(D53+D104-D111)&lt;0.01,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
+        <f>IF(ABS(D105-D111)&lt;0.01,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113"/>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
@@ -3826,6 +3829,7 @@
         <v/>
       </c>
     </row>
+    <row r="121"/>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
@@ -3945,6 +3949,7 @@
         <v/>
       </c>
     </row>
+    <row r="126"/>
     <row r="127">
       <c r="A127" s="18" t="inlineStr">
         <is>

--- a/deliverables/deliverables-20260120-0030/Model_4_Transmission.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_4_Transmission.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,6 +77,10 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="000066CC"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -128,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -169,6 +173,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -624,72 +635,647 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
+    <col width="95" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Transmission - INTUITION MAP</t>
+      <c r="A1">
+        <f>==========================================================================</f>
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>LOTUS INFRASTRUCTURE PARTNERS</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="27" t="inlineStr">
-        <is>
-          <t>WHAT THIS MODEL DOES</t>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>CASE STUDY: ELECTRIC TRANSMISSION LINE ACQUISITION</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regulated transmission - FERC ROE on rate base.</t>
-        </is>
+      <c r="A4">
+        <f>==========================================================================</f>
+        <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr">
-        <is>
-          <t>KEY VALUE DRIVERS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1. FERC ROE</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TIME: 4 Hours | DATE: January 2026 | DELIVERABLES: Model + IC Memo</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2. Rate Base</t>
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>--- MODEL TIMELINE ---</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3. Construction Timing</t>
+          <t>Year 0 (2025): Development costs; construction loan drawn</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Year 1 (2026): Major construction; AFUDC accrues</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
-        <is>
-          <t>DEBT STRUCTURE RATIONALE</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Year 2 (2027): Construction completion</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sculpted 1.40x - regulated returns.</t>
+          <t>Year 3 (2028): COD - Term debt takeout; tariff revenue starts</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Year 10 (2035): Model horizon (asset life 40+ years)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="27" t="inlineStr">
+        <is>
+          <t>--- SITUATION ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>Lotus Infrastructure Partners is evaluating equity investment in a
+150-mile, 345 kV transmission line under development in SPP. FERC has
+approved 10.5% ROE with 50/50 regulatory capital structure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>Development began in 2025 (Y0), with construction in 2026-2027 and COD
+expected in Year 3 (2028). Total project cost is ~$585mm including
+development, construction, and AFUDC during construction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="inlineStr">
+        <is>
+          <t>Upon COD, revenue comes from FERC-approved tariff based on rate base and
+allowed ROE. The line has 40+ years expected useful life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>Lotus is offered $180mm equity during construction. Commitment needed by
+March 15, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="27" t="inlineStr">
+        <is>
+          <t>--- KEY VALUE DRIVERS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>* FERC ROE: Allowed return on equity sets revenue requirement</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>* Rate Base: Capital invested that earns the allowed return</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>* Construction Timing: Delays reduce returns; AFUDC accrues during build</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>* Regulatory Risk: ROE can change in FERC rate case proceedings</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="27" t="inlineStr">
+        <is>
+          <t>--- STEP-BY-STEP MODEL BUILDING GUIDE ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="29" t="inlineStr">
+        <is>
+          <t>STEP-BY-STEP MODEL BUILDING GUIDE FOR TRANSMISSION</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="29" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="29" t="inlineStr">
+        <is>
+          <t>KEY DIFFERENCES:</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="29" t="inlineStr">
+        <is>
+          <t>- CONSTRUCTION PERIOD before operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="29" t="inlineStr">
+        <is>
+          <t>- AFUDC (capitalized interest) accrues to rate base</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="29" t="inlineStr">
+        <is>
+          <t>- Revenue is REGULATED formula, not market prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="29" t="inlineStr">
+        <is>
+          <t>- Two financing events: Construction loan -&gt; Term debt takeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="29" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="29" t="inlineStr">
+        <is>
+          <t>1. CONSTRUCTION PERIOD (Years 0-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Development Costs: $35mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Construction Costs: $550mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Construction Loan: 85% of construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   AFUDC = Const Loan x Interest x Avg Period = ~$35mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   AFUDC accrues to Rate Base (non-cash during construction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="29" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="29" t="inlineStr">
+        <is>
+          <t>2. RATE BASE AT COD (Year 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Rate Base = Development + Construction + AFUDC</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   = $35mm + $550mm + ~$35mm = ~$620mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="29" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="29" t="inlineStr">
+        <is>
+          <t>3. TERM DEBT TAKEOUT AT COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   At COD, Construction Loan repaid by Term Debt</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Term Debt = Rate Base x Regulatory Debt % = $620mm x 50% = $310mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Use RATE BASE (not construction cost) for debt sizing</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="29" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="29" t="inlineStr">
+        <is>
+          <t>4. REVENUE CALCULATION (Years 3+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Revenue = Rate Base x (ROE + Depreciation/Life + O&amp;M/RB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="29" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="29" t="inlineStr">
+        <is>
+          <t>5. S&amp;U - TWO EVENTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   At Close (Y0): Development costs, fees -&gt; Const loan, equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   At COD (Y3): Const loan payoff -&gt; Term debt, permanent equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   DSRA is a USE (funded by debt/equity), NOT a Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="29" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="29" t="inlineStr">
+        <is>
+          <t>6. SCULPTED DEBT</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Regulated cash flows support sculpted debt at 1.40x DSCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="27" t="inlineStr">
+        <is>
+          <t>--- HOW TO AVOID CIRCULARITY ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>TRANSMISSION - SPECIAL CONSIDERATIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>No sweep mechanics - sculpted debt only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>AFUDC creates complexity but not circularity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>S&amp;U RULES:</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>- DSRA is a Use, NOT a Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>- Balance check compares Total Uses vs Total Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>- Construction loan payoff must be included at COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="27" t="inlineStr">
+        <is>
+          <t>--- ALTERNATIVE SCENARIOS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ALTERNATIVE SCENARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>A. Acquisition at COD (No Construction):</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Skip construction period</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Buy operating asset at Rate Base multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>B. Rate Case During Hold:</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - ROE may change in rate proceedings</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Model +/- 50bp ROE sensitivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>C. Rate Base Growth:</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Capital additions over time</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Growing rate base = growing earnings</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="27" t="inlineStr">
+        <is>
+          <t>--- QA CHECKS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>QA CHECKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1. AFUDC included in Rate Base at COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2. S&amp;U balances at BOTH close and COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>3. DSRA is only a Use, never a Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>4. Revenue ties to rate base x allowed returns</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>5. ROE sensitivity shows material impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="27" t="inlineStr">
+        <is>
+          <t>--- HINTS &amp; PITFALLS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="30" t="inlineStr">
+        <is>
+          <t>* AFUDC is often $20-40mm - don't forget to capitalize it</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="30" t="inlineStr">
+        <is>
+          <t>* 50bp ROE change at 10x rate base = 5% equity value impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="30" t="inlineStr">
+        <is>
+          <t>* Construction delays kill returns - model delay scenarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="30" t="inlineStr">
+        <is>
+          <t>* DSRA is a Use funded by debt/equity, NOT a source</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="27" t="inlineStr">
+        <is>
+          <t>--- INTERVIEW QUESTIONS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Q: Walk me through AFUDC and how it affects rate base at COD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Q: How does a 50bp ROE change affect your equity returns?</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Q: What construction risks would you prioritize in diligence?</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Q: How would you structure the construction loan takeout?</t>
         </is>
       </c>
     </row>
@@ -1063,38 +1649,60 @@
           <t>Transmission Model - Lotus Infrastructure Partners</t>
         </is>
       </c>
-      <c r="D1" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H1" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I1" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J1" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K1" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="L1" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M1" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="N1" s="2" t="n">
-        <v>10</v>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Y0 (2025)</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Y1 (2026)</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
+        <is>
+          <t>Y2 (2027)</t>
+        </is>
+      </c>
+      <c r="G1" s="28" t="inlineStr">
+        <is>
+          <t>Y3 (2028)</t>
+        </is>
+      </c>
+      <c r="H1" s="28" t="inlineStr">
+        <is>
+          <t>Y4 (2029)</t>
+        </is>
+      </c>
+      <c r="I1" s="28" t="inlineStr">
+        <is>
+          <t>Y5 (2030)</t>
+        </is>
+      </c>
+      <c r="J1" s="28" t="inlineStr">
+        <is>
+          <t>Y6 (2031)</t>
+        </is>
+      </c>
+      <c r="K1" s="28" t="inlineStr">
+        <is>
+          <t>Y7 (2032)</t>
+        </is>
+      </c>
+      <c r="L1" s="28" t="inlineStr">
+        <is>
+          <t>Y8 (2033)</t>
+        </is>
+      </c>
+      <c r="M1" s="28" t="inlineStr">
+        <is>
+          <t>Y9 (2034)</t>
+        </is>
+      </c>
+      <c r="N1" s="28" t="inlineStr">
+        <is>
+          <t>Y10 (2035)</t>
+        </is>
       </c>
     </row>
     <row r="2">
@@ -3459,7 +4067,6 @@
         <v/>
       </c>
     </row>
-    <row r="97"/>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
@@ -3591,7 +4198,6 @@
         <v/>
       </c>
     </row>
-    <row r="106"/>
     <row r="107">
       <c r="A107" s="18" t="inlineStr">
         <is>
@@ -3682,7 +4288,6 @@
         <v/>
       </c>
     </row>
-    <row r="113"/>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
@@ -3829,7 +4434,6 @@
         <v/>
       </c>
     </row>
-    <row r="121"/>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
@@ -3949,7 +4553,6 @@
         <v/>
       </c>
     </row>
-    <row r="126"/>
     <row r="127">
       <c r="A127" s="18" t="inlineStr">
         <is>

--- a/deliverables/deliverables-20260120-0030/Model_4_Transmission.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_4_Transmission.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -105,6 +105,12 @@
       <color rgb="001F4E79"/>
       <sz val="12"/>
     </font>
+    <font/>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -156,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -215,6 +221,14 @@
     <xf numFmtId="165" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1148,7 +1162,6 @@
         </is>
       </c>
     </row>
-    <row r="68"/>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
@@ -1163,7 +1176,6 @@
         </is>
       </c>
     </row>
-    <row r="71"/>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
@@ -1206,7 +1218,6 @@
         </is>
       </c>
     </row>
-    <row r="79"/>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
@@ -1228,7 +1239,6 @@
         </is>
       </c>
     </row>
-    <row r="83"/>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
@@ -1250,7 +1260,6 @@
         </is>
       </c>
     </row>
-    <row r="87"/>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
@@ -1286,7 +1295,6 @@
         </is>
       </c>
     </row>
-    <row r="94"/>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
@@ -1842,7 +1850,6 @@
           <t>4:00</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="34" t="inlineStr">
@@ -3463,216 +3470,196 @@
     <row r="5">
       <c r="A5" s="31" t="inlineStr">
         <is>
-          <t>═══════════════════ CONTROL PANEL ═══════════════════</t>
-        </is>
-      </c>
+          <t>═══════════ CONTROL PANEL ═══════════</t>
+        </is>
+      </c>
+      <c r="B5" s="42" t="n"/>
+      <c r="C5" s="42" t="n"/>
+      <c r="D5" s="42" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="42" t="n"/>
+      <c r="B6" s="42" t="n"/>
+      <c r="C6" s="42" t="n"/>
+      <c r="D6" s="42" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr">
-        <is>
-          <t>Revenue Mode</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Merchant / Contracted / Hybrid</t>
-        </is>
-      </c>
-      <c r="D7" s="40" t="inlineStr">
-        <is>
-          <t>Merchant</t>
-        </is>
-      </c>
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
+      <c r="B7" s="42" t="n"/>
+      <c r="C7" s="42" t="n"/>
+      <c r="D7" s="42" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="27" t="inlineStr">
         <is>
-          <t>Contract Years</t>
-        </is>
-      </c>
+          <t>Revenue Mode</t>
+        </is>
+      </c>
+      <c r="B8" s="42" t="n"/>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>If Hybrid: years of contracted revenue</t>
+          <t>Merchant / Contracted / Hybrid</t>
         </is>
       </c>
       <c r="D8" s="40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Merchant</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="27" t="inlineStr">
         <is>
+          <t>Contract End Year</t>
+        </is>
+      </c>
+      <c r="B9" s="42" t="n"/>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>0 = pure merchant; else year PPA ends</t>
+        </is>
+      </c>
+      <c r="D9" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="42" t="n"/>
+      <c r="B10" s="42" t="n"/>
+      <c r="C10" s="42" t="n"/>
+      <c r="D10" s="42" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>TIMING</t>
+        </is>
+      </c>
+      <c r="B11" s="42" t="n"/>
+      <c r="C11" s="42" t="n"/>
+      <c r="D11" s="42" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>Exit Year</t>
+        </is>
+      </c>
+      <c r="B12" s="42" t="n"/>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>5 / 7 / 10</t>
+        </is>
+      </c>
+      <c r="D12" s="40" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>Tax Credit End Year</t>
+        </is>
+      </c>
+      <c r="B13" s="42" t="n"/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>0 = N/A; else last year of PTC/ITC</t>
+        </is>
+      </c>
+      <c r="D13" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="42" t="n"/>
+      <c r="B14" s="42" t="n"/>
+      <c r="C14" s="42" t="n"/>
+      <c r="D14" s="42" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>DEBT</t>
+        </is>
+      </c>
+      <c r="B15" s="42" t="n"/>
+      <c r="C15" s="42" t="n"/>
+      <c r="D15" s="44" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
           <t>Debt Sweep</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>ON / OFF</t>
-        </is>
-      </c>
-      <c r="D9" s="40" t="inlineStr">
+      <c r="B16" s="42" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ON / OFF (for sweep assets)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="27" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>Sweep %</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Only active if Sweep = ON</t>
-        </is>
-      </c>
-      <c r="D10" s="40" t="inlineStr">
+      <c r="B17" s="42" t="n"/>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Active when Sweep = ON</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="42" t="n"/>
+      <c r="B18" s="42" t="n"/>
+      <c r="C18" s="42" t="n"/>
+      <c r="D18" s="45" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="43" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="B19" s="42" t="n"/>
+      <c r="C19" s="42" t="n"/>
+      <c r="D19" s="46" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="47" t="inlineStr">
         <is>
           <t>Exit Method</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="B20" s="42" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Multiple / DCF</t>
         </is>
       </c>
-      <c r="D11" s="40" t="inlineStr">
+      <c r="D20" s="40" t="inlineStr">
         <is>
           <t>Multiple</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="31" t="inlineStr">
-        <is>
-          <t>════════════════════════════════════════════════════</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Avg CFADS (Y3-Y10)</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>EBITDA minus Taxes</t>
-        </is>
-      </c>
-      <c r="D15" s="7">
-        <f>AVERAGE(G76:N76)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Min DSCR (Y3-Y10)</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>CFADS / Debt Service</t>
-        </is>
-      </c>
-      <c r="D16" s="19">
-        <f>IF(COUNTIF(G85:N85,"&gt;0")&gt;0,MINIFS(G85:N85,G85:N85,"&gt;0"),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Levered IRR</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>IRR of Equity CFs</t>
-        </is>
-      </c>
-      <c r="D17" s="20">
-        <f>D124</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>MOIC</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Total In / Total Out</t>
-        </is>
-      </c>
-      <c r="D18" s="19">
-        <f>D125</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Unlevered IRR</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>IRR of Equity CFs</t>
-        </is>
-      </c>
-      <c r="D19" s="20">
-        <f>D129</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>═══ QA CHECKS ═══</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
@@ -3685,9 +3672,9 @@
       <c r="N20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>S&amp;U Balance</t>
+      <c r="A21" s="31" t="inlineStr">
+        <is>
+          <t>════════════════════════════════════</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr"/>
@@ -3727,8 +3714,6 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
@@ -3829,7 +3814,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
@@ -3910,7 +3894,6 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
@@ -3971,7 +3954,6 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
@@ -4032,7 +4014,6 @@
         <v>0.025</v>
       </c>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
@@ -4173,7 +4154,6 @@
         <v>1.15</v>
       </c>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
@@ -4234,7 +4214,6 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56"/>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
@@ -4275,7 +4254,6 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="59"/>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
@@ -4401,7 +4379,6 @@
         <v/>
       </c>
     </row>
-    <row r="66"/>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
@@ -4515,7 +4492,6 @@
         <v/>
       </c>
     </row>
-    <row r="73"/>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
@@ -4593,7 +4569,6 @@
         <v/>
       </c>
     </row>
-    <row r="76"/>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
@@ -4708,7 +4683,6 @@
         <v/>
       </c>
     </row>
-    <row r="79"/>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
@@ -4766,7 +4740,6 @@
         <v/>
       </c>
     </row>
-    <row r="81"/>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
@@ -5015,7 +4988,6 @@
         <v/>
       </c>
     </row>
-    <row r="87"/>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
@@ -5431,7 +5403,6 @@
         <v/>
       </c>
     </row>
-    <row r="96"/>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
@@ -5692,7 +5663,6 @@
         <v/>
       </c>
     </row>
-    <row r="102"/>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
@@ -5880,7 +5850,6 @@
         <v/>
       </c>
     </row>
-    <row r="107"/>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
@@ -6012,7 +5981,6 @@
         <v/>
       </c>
     </row>
-    <row r="116"/>
     <row r="117">
       <c r="A117" s="18" t="inlineStr">
         <is>
@@ -6103,7 +6071,6 @@
         <v/>
       </c>
     </row>
-    <row r="123"/>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
@@ -6250,7 +6217,6 @@
         <v/>
       </c>
     </row>
-    <row r="131"/>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
@@ -6370,7 +6336,6 @@
         <v/>
       </c>
     </row>
-    <row r="136"/>
     <row r="137">
       <c r="A137" s="18" t="inlineStr">
         <is>
@@ -6623,216 +6588,196 @@
     <row r="5">
       <c r="A5" s="31" t="inlineStr">
         <is>
-          <t>═══════════════════ CONTROL PANEL ═══════════════════</t>
-        </is>
-      </c>
+          <t>═══════════ CONTROL PANEL ═══════════</t>
+        </is>
+      </c>
+      <c r="B5" s="42" t="n"/>
+      <c r="C5" s="42" t="n"/>
+      <c r="D5" s="42" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="42" t="n"/>
+      <c r="B6" s="42" t="n"/>
+      <c r="C6" s="42" t="n"/>
+      <c r="D6" s="42" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr">
-        <is>
-          <t>Revenue Mode</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Merchant / Contracted / Hybrid</t>
-        </is>
-      </c>
-      <c r="D7" s="40" t="inlineStr">
-        <is>
-          <t>Merchant</t>
-        </is>
-      </c>
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
+      <c r="B7" s="42" t="n"/>
+      <c r="C7" s="42" t="n"/>
+      <c r="D7" s="42" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="27" t="inlineStr">
         <is>
-          <t>Contract Years</t>
-        </is>
-      </c>
+          <t>Revenue Mode</t>
+        </is>
+      </c>
+      <c r="B8" s="42" t="n"/>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>If Hybrid: years of contracted revenue</t>
+          <t>Merchant / Contracted / Hybrid</t>
         </is>
       </c>
       <c r="D8" s="40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Merchant</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="27" t="inlineStr">
         <is>
+          <t>Contract End Year</t>
+        </is>
+      </c>
+      <c r="B9" s="42" t="n"/>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>0 = pure merchant; else year PPA ends</t>
+        </is>
+      </c>
+      <c r="D9" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="42" t="n"/>
+      <c r="B10" s="42" t="n"/>
+      <c r="C10" s="42" t="n"/>
+      <c r="D10" s="42" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>TIMING</t>
+        </is>
+      </c>
+      <c r="B11" s="42" t="n"/>
+      <c r="C11" s="42" t="n"/>
+      <c r="D11" s="42" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>Exit Year</t>
+        </is>
+      </c>
+      <c r="B12" s="42" t="n"/>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>5 / 7 / 10</t>
+        </is>
+      </c>
+      <c r="D12" s="40" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>Tax Credit End Year</t>
+        </is>
+      </c>
+      <c r="B13" s="42" t="n"/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>0 = N/A; else last year of PTC/ITC</t>
+        </is>
+      </c>
+      <c r="D13" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="42" t="n"/>
+      <c r="B14" s="42" t="n"/>
+      <c r="C14" s="42" t="n"/>
+      <c r="D14" s="42" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>DEBT</t>
+        </is>
+      </c>
+      <c r="B15" s="42" t="n"/>
+      <c r="C15" s="42" t="n"/>
+      <c r="D15" s="44" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
           <t>Debt Sweep</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>ON / OFF</t>
-        </is>
-      </c>
-      <c r="D9" s="40" t="inlineStr">
+      <c r="B16" s="42" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ON / OFF (for sweep assets)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="27" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>Sweep %</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Only active if Sweep = ON</t>
-        </is>
-      </c>
-      <c r="D10" s="40" t="inlineStr">
+      <c r="B17" s="42" t="n"/>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Active when Sweep = ON</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="42" t="n"/>
+      <c r="B18" s="42" t="n"/>
+      <c r="C18" s="42" t="n"/>
+      <c r="D18" s="45" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="43" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="B19" s="42" t="n"/>
+      <c r="C19" s="42" t="n"/>
+      <c r="D19" s="46" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="47" t="inlineStr">
         <is>
           <t>Exit Method</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="B20" s="42" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Multiple / DCF</t>
         </is>
       </c>
-      <c r="D11" s="40" t="inlineStr">
+      <c r="D20" s="40" t="inlineStr">
         <is>
           <t>Multiple</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="31" t="inlineStr">
-        <is>
-          <t>════════════════════════════════════════════════════</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Avg CFADS (Y3-Y10)</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>EBITDA minus Taxes</t>
-        </is>
-      </c>
-      <c r="D15" s="7">
-        <f>AVERAGE(G76:N76)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Min DSCR (Y3-Y10)</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>CFADS / Debt Service</t>
-        </is>
-      </c>
-      <c r="D16" s="19">
-        <f>IF(COUNTIF(G85:N85,"&gt;0")&gt;0,MINIFS(G85:N85,G85:N85,"&gt;0"),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Levered IRR</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>IRR of Equity CFs</t>
-        </is>
-      </c>
-      <c r="D17" s="20">
-        <f>D124</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>MOIC</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Total In / Total Out</t>
-        </is>
-      </c>
-      <c r="D18" s="19">
-        <f>D125</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Unlevered IRR</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>IRR of Equity CFs</t>
-        </is>
-      </c>
-      <c r="D19" s="20">
-        <f>D129</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>═══ QA CHECKS ═══</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
@@ -6845,9 +6790,9 @@
       <c r="N20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>S&amp;U Balance</t>
+      <c r="A21" s="31" t="inlineStr">
+        <is>
+          <t>════════════════════════════════════</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr"/>
@@ -6887,8 +6832,6 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
@@ -6989,7 +6932,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
@@ -7070,7 +7012,6 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
@@ -7131,7 +7072,6 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
@@ -7192,7 +7132,6 @@
         <v>0.025</v>
       </c>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
@@ -7333,7 +7272,6 @@
         <v>1.15</v>
       </c>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
@@ -7394,7 +7332,6 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56"/>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
@@ -7435,7 +7372,6 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="59"/>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
@@ -7561,7 +7497,6 @@
         <v/>
       </c>
     </row>
-    <row r="66"/>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
@@ -7675,7 +7610,6 @@
         <v/>
       </c>
     </row>
-    <row r="73"/>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
@@ -7753,7 +7687,6 @@
         <v/>
       </c>
     </row>
-    <row r="76"/>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
@@ -7868,7 +7801,6 @@
         <v/>
       </c>
     </row>
-    <row r="79"/>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
@@ -7926,7 +7858,6 @@
         <v/>
       </c>
     </row>
-    <row r="81"/>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
@@ -8175,7 +8106,6 @@
         <v/>
       </c>
     </row>
-    <row r="87"/>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
@@ -8591,7 +8521,6 @@
         <v/>
       </c>
     </row>
-    <row r="96"/>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
@@ -8852,7 +8781,6 @@
         <v/>
       </c>
     </row>
-    <row r="102"/>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
@@ -9040,7 +8968,6 @@
         <v/>
       </c>
     </row>
-    <row r="107"/>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
@@ -9172,7 +9099,6 @@
         <v/>
       </c>
     </row>
-    <row r="116"/>
     <row r="117">
       <c r="A117" s="18" t="inlineStr">
         <is>
@@ -9319,7 +9245,6 @@
         <v/>
       </c>
     </row>
-    <row r="129"/>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
@@ -9466,7 +9391,6 @@
         <v/>
       </c>
     </row>
-    <row r="137"/>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
@@ -9586,7 +9510,6 @@
         <v/>
       </c>
     </row>
-    <row r="142"/>
     <row r="143">
       <c r="A143" s="18" t="inlineStr">
         <is>

--- a/deliverables/deliverables-20260120-0030/Model_4_Transmission.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_4_Transmission.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -111,6 +111,14 @@
       <i val="1"/>
       <color rgb="00666666"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -162,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -229,6 +237,8 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3445,6 +3455,11 @@
         <f>$D$53</f>
         <v/>
       </c>
+      <c r="M3" s="48" t="inlineStr">
+        <is>
+          <t>IRR Sensitivity:</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -3465,6 +3480,11 @@
       <c r="D4" s="7">
         <f>G70</f>
         <v/>
+      </c>
+      <c r="M4" s="49" t="inlineStr">
+        <is>
+          <t>+/- 5% Entry → ~+/- 1% IRR</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -3476,6 +3496,11 @@
       <c r="B5" s="42" t="n"/>
       <c r="C5" s="42" t="n"/>
       <c r="D5" s="42" t="n"/>
+      <c r="M5" s="49" t="inlineStr">
+        <is>
+          <t>+/- 0.5x Exit → ~+/- 1.5% IRR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="42" t="n"/>
@@ -3714,6 +3739,8 @@
         <v/>
       </c>
     </row>
+    <row r="24"/>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
@@ -3814,6 +3841,7 @@
         <v>3</v>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
@@ -3894,6 +3922,7 @@
         <v>40</v>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
@@ -3954,6 +3983,7 @@
         <v>0.02</v>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
@@ -4014,6 +4044,7 @@
         <v>0.025</v>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
@@ -4154,6 +4185,7 @@
         <v>1.15</v>
       </c>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
@@ -4214,6 +4246,7 @@
         <v>10</v>
       </c>
     </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
@@ -4254,6 +4287,7 @@
         <v>0.25</v>
       </c>
     </row>
+    <row r="59"/>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
@@ -4379,6 +4413,7 @@
         <v/>
       </c>
     </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
@@ -4492,6 +4527,7 @@
         <v/>
       </c>
     </row>
+    <row r="73"/>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
@@ -4569,6 +4605,7 @@
         <v/>
       </c>
     </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
@@ -4683,6 +4720,7 @@
         <v/>
       </c>
     </row>
+    <row r="79"/>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
@@ -4740,6 +4778,7 @@
         <v/>
       </c>
     </row>
+    <row r="81"/>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
@@ -4988,6 +5027,7 @@
         <v/>
       </c>
     </row>
+    <row r="87"/>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
@@ -5403,6 +5443,7 @@
         <v/>
       </c>
     </row>
+    <row r="96"/>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
@@ -5663,6 +5704,7 @@
         <v/>
       </c>
     </row>
+    <row r="102"/>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
@@ -5850,6 +5892,7 @@
         <v/>
       </c>
     </row>
+    <row r="107"/>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
@@ -5981,6 +6024,7 @@
         <v/>
       </c>
     </row>
+    <row r="116"/>
     <row r="117">
       <c r="A117" s="18" t="inlineStr">
         <is>
@@ -6071,6 +6115,7 @@
         <v/>
       </c>
     </row>
+    <row r="123"/>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
@@ -6217,6 +6262,7 @@
         <v/>
       </c>
     </row>
+    <row r="131"/>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
@@ -6336,6 +6382,7 @@
         <v/>
       </c>
     </row>
+    <row r="136"/>
     <row r="137">
       <c r="A137" s="18" t="inlineStr">
         <is>

--- a/deliverables/deliverables-20260120-0030/Model_4_Transmission.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_4_Transmission.xlsx
@@ -170,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -239,6 +239,10 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3452,7 +3456,7 @@
       </c>
       <c r="C3" s="6" t="inlineStr"/>
       <c r="D3" s="7">
-        <f>$D$53</f>
+        <f>$D$63</f>
         <v/>
       </c>
       <c r="M3" s="48" t="inlineStr">
@@ -3478,7 +3482,7 @@
         </is>
       </c>
       <c r="D4" s="7">
-        <f>G70</f>
+        <f>G80</f>
         <v/>
       </c>
       <c r="M4" s="49" t="inlineStr">
@@ -3739,8 +3743,6 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
@@ -3841,7 +3843,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
@@ -3922,7 +3923,6 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
@@ -3983,7 +3983,6 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
@@ -4044,7 +4043,6 @@
         <v>0.025</v>
       </c>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
@@ -4185,7 +4183,6 @@
         <v>1.15</v>
       </c>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
@@ -4246,7 +4243,6 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56"/>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
@@ -4287,7 +4283,6 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="59"/>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
@@ -4325,7 +4320,7 @@
         </is>
       </c>
       <c r="D61" s="15">
-        <f>$D$19*$D$36</f>
+        <f>$D$29*$D$46</f>
         <v/>
       </c>
     </row>
@@ -4346,7 +4341,7 @@
         </is>
       </c>
       <c r="D62" s="15">
-        <f>$D$51*$D$38</f>
+        <f>$D$61*$D$48</f>
         <v/>
       </c>
     </row>
@@ -4367,7 +4362,7 @@
         </is>
       </c>
       <c r="D63" s="15">
-        <f>$D$17+$D$18+$D$19+$D$52</f>
+        <f>$D$27+$D$28+$D$29+$D$62</f>
         <v/>
       </c>
     </row>
@@ -4388,7 +4383,7 @@
         </is>
       </c>
       <c r="D64" s="15">
-        <f>$D$53*$D$37</f>
+        <f>$D$63*$D$47</f>
         <v/>
       </c>
     </row>
@@ -4409,11 +4404,10 @@
         </is>
       </c>
       <c r="D65" s="15">
-        <f>$D$53/$D$25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66"/>
+        <f>$D$63/$D$35</f>
+        <v/>
+      </c>
+    </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
@@ -4447,7 +4441,7 @@
       </c>
       <c r="C68" s="6" t="inlineStr"/>
       <c r="D68" s="16">
-        <f>$D$17</f>
+        <f>$D$27</f>
         <v/>
       </c>
     </row>
@@ -4464,7 +4458,7 @@
       </c>
       <c r="C69" s="6" t="inlineStr"/>
       <c r="E69" s="16">
-        <f>$D$18</f>
+        <f>$D$28</f>
         <v/>
       </c>
     </row>
@@ -4485,7 +4479,7 @@
         </is>
       </c>
       <c r="F70" s="16">
-        <f>$D$19*(1-$D$36)</f>
+        <f>$D$29-$D$61</f>
         <v/>
       </c>
     </row>
@@ -4506,7 +4500,7 @@
         </is>
       </c>
       <c r="G71" s="16">
-        <f>($D$51+$D$52)-$D$54</f>
+        <f>$D$61-$D$64</f>
         <v/>
       </c>
     </row>
@@ -4523,11 +4517,10 @@
       </c>
       <c r="C72" s="6" t="inlineStr"/>
       <c r="D72" s="7">
-        <f>D58+E59+F60+G61</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73"/>
+        <f>D68+E69+F70+G71</f>
+        <v/>
+      </c>
+    </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
@@ -4564,48 +4557,85 @@
           <t>Escalated</t>
         </is>
       </c>
-      <c r="E75" s="15">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F75" s="15">
-        <f>0</f>
-        <v/>
+      <c r="E75" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="G75" s="15">
-        <f>$D$28*(1+$D$29)^(3-3)</f>
+        <f>$D$38*(1+$D$39)^(1-1)</f>
         <v/>
       </c>
       <c r="H75" s="15">
-        <f>$D$28*(1+$D$29)^(4-3)</f>
+        <f>$D$38*(1+$D$39)^(2-1)</f>
         <v/>
       </c>
       <c r="I75" s="15">
-        <f>$D$28*(1+$D$29)^(5-3)</f>
+        <f>$D$38*(1+$D$39)^(3-1)</f>
         <v/>
       </c>
       <c r="J75" s="15">
-        <f>$D$28*(1+$D$29)^(6-3)</f>
+        <f>$D$38*(1+$D$39)^(4-1)</f>
         <v/>
       </c>
       <c r="K75" s="15">
-        <f>$D$28*(1+$D$29)^(7-3)</f>
+        <f>$D$38*(1+$D$39)^(5-1)</f>
         <v/>
       </c>
       <c r="L75" s="15">
-        <f>$D$28*(1+$D$29)^(8-3)</f>
+        <f>$D$38*(1+$D$39)^(6-1)</f>
         <v/>
       </c>
       <c r="M75" s="15">
-        <f>$D$28*(1+$D$29)^(9-3)</f>
+        <f>$D$38*(1+$D$39)^(7-1)</f>
         <v/>
       </c>
       <c r="N75" s="15">
-        <f>$D$28*(1+$D$29)^(10-3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76"/>
+        <f>$D$38*(1+$D$39)^(8-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <f>$D$33*$D$34*G75/1000</f>
+        <v/>
+      </c>
+      <c r="H76">
+        <f>$D$33*$D$34*H75/1000</f>
+        <v/>
+      </c>
+      <c r="I76">
+        <f>$D$33*$D$34*I75/1000</f>
+        <v/>
+      </c>
+      <c r="J76">
+        <f>$D$33*$D$34*J75/1000</f>
+        <v/>
+      </c>
+      <c r="K76">
+        <f>$D$33*$D$34*K75/1000</f>
+        <v/>
+      </c>
+      <c r="L76">
+        <f>$D$33*$D$34*L75/1000</f>
+        <v/>
+      </c>
+      <c r="M76">
+        <f>$D$33*$D$34*M75/1000</f>
+        <v/>
+      </c>
+      <c r="N76">
+        <f>$D$33*$D$34*N75/1000</f>
+        <v/>
+      </c>
+    </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
@@ -4622,44 +4652,42 @@
           <t>Cap × Tariff × Avail × 1000/1M</t>
         </is>
       </c>
-      <c r="E77" s="15">
-        <f>$D$23*E65*$D$24*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="F77" s="15">
-        <f>$D$23*F65*$D$24*1000/1000000</f>
-        <v/>
+      <c r="E77" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="G77" s="15">
-        <f>$D$23*G65*$D$24*1000/1000000</f>
+        <f>$D$33*$D$34*G75/1000</f>
         <v/>
       </c>
       <c r="H77" s="15">
-        <f>$D$23*H65*$D$24*1000/1000000</f>
+        <f>$D$33*$D$34*H75/1000</f>
         <v/>
       </c>
       <c r="I77" s="15">
-        <f>$D$23*I65*$D$24*1000/1000000</f>
+        <f>$D$33*$D$34*I75/1000</f>
         <v/>
       </c>
       <c r="J77" s="15">
-        <f>$D$23*J65*$D$24*1000/1000000</f>
+        <f>$D$33*$D$34*J75/1000</f>
         <v/>
       </c>
       <c r="K77" s="15">
-        <f>$D$23*K65*$D$24*1000/1000000</f>
+        <f>$D$33*$D$34*K75/1000</f>
         <v/>
       </c>
       <c r="L77" s="15">
-        <f>$D$23*L65*$D$24*1000/1000000</f>
+        <f>$D$33*$D$34*L75/1000</f>
         <v/>
       </c>
       <c r="M77" s="15">
-        <f>$D$23*M65*$D$24*1000/1000000</f>
+        <f>$D$33*$D$34*M75/1000</f>
         <v/>
       </c>
       <c r="N77" s="15">
-        <f>$D$23*N65*$D$24*1000/1000000</f>
+        <f>$D$33*$D$34*N75/1000</f>
         <v/>
       </c>
     </row>
@@ -4679,48 +4707,85 @@
           <t>Post-COD only</t>
         </is>
       </c>
-      <c r="E78" s="15">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F78" s="15">
-        <f>0</f>
-        <v/>
+      <c r="E78" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="G78" s="15">
-        <f>$D$32*(1+$D$33)^(3-3)</f>
+        <f>$D$42*(1+$D$43)^(1-1)</f>
         <v/>
       </c>
       <c r="H78" s="15">
-        <f>$D$32*(1+$D$33)^(4-3)</f>
+        <f>$D$42*(1+$D$43)^(2-1)</f>
         <v/>
       </c>
       <c r="I78" s="15">
-        <f>$D$32*(1+$D$33)^(5-3)</f>
+        <f>$D$42*(1+$D$43)^(3-1)</f>
         <v/>
       </c>
       <c r="J78" s="15">
-        <f>$D$32*(1+$D$33)^(6-3)</f>
+        <f>$D$42*(1+$D$43)^(4-1)</f>
         <v/>
       </c>
       <c r="K78" s="15">
-        <f>$D$32*(1+$D$33)^(7-3)</f>
+        <f>$D$42*(1+$D$43)^(5-1)</f>
         <v/>
       </c>
       <c r="L78" s="15">
-        <f>$D$32*(1+$D$33)^(8-3)</f>
+        <f>$D$42*(1+$D$43)^(6-1)</f>
         <v/>
       </c>
       <c r="M78" s="15">
-        <f>$D$32*(1+$D$33)^(9-3)</f>
+        <f>$D$42*(1+$D$43)^(7-1)</f>
         <v/>
       </c>
       <c r="N78" s="15">
-        <f>$D$32*(1+$D$33)^(10-3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79"/>
+        <f>$D$42*(1+$D$43)^(8-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="50">
+        <f>G76-G77</f>
+        <v/>
+      </c>
+      <c r="H79" s="50">
+        <f>H76-H77</f>
+        <v/>
+      </c>
+      <c r="I79" s="50">
+        <f>I76-I77</f>
+        <v/>
+      </c>
+      <c r="J79" s="50">
+        <f>J76-J77</f>
+        <v/>
+      </c>
+      <c r="K79" s="50">
+        <f>K76-K77</f>
+        <v/>
+      </c>
+      <c r="L79" s="50">
+        <f>L76-L77</f>
+        <v/>
+      </c>
+      <c r="M79" s="50">
+        <f>M76-M77</f>
+        <v/>
+      </c>
+      <c r="N79" s="50">
+        <f>N76-N77</f>
+        <v/>
+      </c>
+    </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
@@ -4737,48 +4802,45 @@
           <t>Revenue minus OpEx</t>
         </is>
       </c>
-      <c r="E80" s="7">
-        <f>E67-E68</f>
-        <v/>
-      </c>
-      <c r="F80" s="7">
-        <f>F67-F68</f>
-        <v/>
+      <c r="E80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="G80" s="7">
-        <f>G67-G68</f>
+        <f>G77-G78</f>
         <v/>
       </c>
       <c r="H80" s="7">
-        <f>H67-H68</f>
+        <f>H77-H78</f>
         <v/>
       </c>
       <c r="I80" s="7">
-        <f>I67-I68</f>
+        <f>I77-I78</f>
         <v/>
       </c>
       <c r="J80" s="7">
-        <f>J67-J68</f>
+        <f>J77-J78</f>
         <v/>
       </c>
       <c r="K80" s="7">
-        <f>K67-K68</f>
+        <f>K77-K78</f>
         <v/>
       </c>
       <c r="L80" s="7">
-        <f>L67-L68</f>
+        <f>L77-L78</f>
         <v/>
       </c>
       <c r="M80" s="7">
-        <f>M67-M68</f>
+        <f>M77-M78</f>
         <v/>
       </c>
       <c r="N80" s="7">
-        <f>N67-N68</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81"/>
+        <f>N77-N78</f>
+        <v/>
+      </c>
+    </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
@@ -4788,16 +4850,44 @@
       <c r="B82" s="4" t="n"/>
       <c r="C82" s="4" t="n"/>
       <c r="D82" s="4" t="n"/>
-      <c r="E82" s="4" t="n"/>
-      <c r="F82" s="4" t="n"/>
-      <c r="G82" s="4" t="n"/>
-      <c r="H82" s="4" t="n"/>
-      <c r="I82" s="4" t="n"/>
-      <c r="J82" s="4" t="n"/>
-      <c r="K82" s="4" t="n"/>
-      <c r="L82" s="4" t="n"/>
-      <c r="M82" s="4" t="n"/>
-      <c r="N82" s="4" t="n"/>
+      <c r="E82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="4">
+        <f>MAX(0,G79-$D$65)*$D$58</f>
+        <v/>
+      </c>
+      <c r="H82" s="4">
+        <f>MAX(0,H79-$D$65)*$D$58</f>
+        <v/>
+      </c>
+      <c r="I82" s="4">
+        <f>MAX(0,I79-$D$65)*$D$58</f>
+        <v/>
+      </c>
+      <c r="J82" s="4">
+        <f>MAX(0,J79-$D$65)*$D$58</f>
+        <v/>
+      </c>
+      <c r="K82" s="4">
+        <f>MAX(0,K79-$D$65)*$D$58</f>
+        <v/>
+      </c>
+      <c r="L82" s="4">
+        <f>MAX(0,L79-$D$65)*$D$58</f>
+        <v/>
+      </c>
+      <c r="M82" s="4">
+        <f>MAX(0,M79-$D$65)*$D$58</f>
+        <v/>
+      </c>
+      <c r="N82" s="4">
+        <f>MAX(0,N79-$D$65)*$D$58</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -4815,44 +4905,42 @@
           <t>Post-COD only</t>
         </is>
       </c>
-      <c r="E83" s="15">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F83" s="15">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G83" s="15">
-        <f>$D$55</f>
-        <v/>
-      </c>
-      <c r="H83" s="15">
-        <f>$D$55</f>
-        <v/>
-      </c>
-      <c r="I83" s="15">
-        <f>$D$55</f>
-        <v/>
-      </c>
-      <c r="J83" s="15">
-        <f>$D$55</f>
-        <v/>
-      </c>
-      <c r="K83" s="15">
-        <f>$D$55</f>
-        <v/>
-      </c>
-      <c r="L83" s="15">
-        <f>$D$55</f>
-        <v/>
-      </c>
-      <c r="M83" s="15">
-        <f>$D$55</f>
-        <v/>
-      </c>
-      <c r="N83" s="15">
-        <f>$D$55</f>
+      <c r="E83" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="7">
+        <f>$D$65</f>
+        <v/>
+      </c>
+      <c r="H83" s="7">
+        <f>$D$65</f>
+        <v/>
+      </c>
+      <c r="I83" s="7">
+        <f>$D$65</f>
+        <v/>
+      </c>
+      <c r="J83" s="7">
+        <f>$D$65</f>
+        <v/>
+      </c>
+      <c r="K83" s="7">
+        <f>$D$65</f>
+        <v/>
+      </c>
+      <c r="L83" s="7">
+        <f>$D$65</f>
+        <v/>
+      </c>
+      <c r="M83" s="7">
+        <f>$D$65</f>
+        <v/>
+      </c>
+      <c r="N83" s="7">
+        <f>$D$65</f>
         <v/>
       </c>
     </row>
@@ -4872,44 +4960,42 @@
           <t>EBITDA - Depreciation</t>
         </is>
       </c>
-      <c r="E84" s="15">
-        <f>E70-E73</f>
-        <v/>
-      </c>
-      <c r="F84" s="15">
-        <f>F70-F73</f>
-        <v/>
+      <c r="E84" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="G84" s="15">
-        <f>G70-G73</f>
+        <f>G80-G83</f>
         <v/>
       </c>
       <c r="H84" s="15">
-        <f>H70-H73</f>
+        <f>H80-H83</f>
         <v/>
       </c>
       <c r="I84" s="15">
-        <f>I70-I73</f>
+        <f>I80-I83</f>
         <v/>
       </c>
       <c r="J84" s="15">
-        <f>J70-J73</f>
+        <f>J80-J83</f>
         <v/>
       </c>
       <c r="K84" s="15">
-        <f>K70-K73</f>
+        <f>K80-K83</f>
         <v/>
       </c>
       <c r="L84" s="15">
-        <f>L70-L73</f>
+        <f>L80-L83</f>
         <v/>
       </c>
       <c r="M84" s="15">
-        <f>M70-M73</f>
+        <f>M80-M83</f>
         <v/>
       </c>
       <c r="N84" s="15">
-        <f>N70-N73</f>
+        <f>N80-N83</f>
         <v/>
       </c>
     </row>
@@ -4929,44 +5015,42 @@
           <t>MAX(0, EBIT) × Tax Rate</t>
         </is>
       </c>
-      <c r="E85" s="15">
-        <f>MAX(0,E74)*$D$48</f>
-        <v/>
-      </c>
-      <c r="F85" s="15">
-        <f>MAX(0,F74)*$D$48</f>
-        <v/>
+      <c r="E85" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="G85" s="15">
-        <f>MAX(0,G74)*$D$48</f>
+        <f>MAX(0,G84)*$D$58</f>
         <v/>
       </c>
       <c r="H85" s="15">
-        <f>MAX(0,H74)*$D$48</f>
+        <f>MAX(0,H84)*$D$58</f>
         <v/>
       </c>
       <c r="I85" s="15">
-        <f>MAX(0,I74)*$D$48</f>
+        <f>MAX(0,I84)*$D$58</f>
         <v/>
       </c>
       <c r="J85" s="15">
-        <f>MAX(0,J74)*$D$48</f>
+        <f>MAX(0,J84)*$D$58</f>
         <v/>
       </c>
       <c r="K85" s="15">
-        <f>MAX(0,K74)*$D$48</f>
+        <f>MAX(0,K84)*$D$58</f>
         <v/>
       </c>
       <c r="L85" s="15">
-        <f>MAX(0,L74)*$D$48</f>
+        <f>MAX(0,L84)*$D$58</f>
         <v/>
       </c>
       <c r="M85" s="15">
-        <f>MAX(0,M74)*$D$48</f>
+        <f>MAX(0,M84)*$D$58</f>
         <v/>
       </c>
       <c r="N85" s="15">
-        <f>MAX(0,N74)*$D$48</f>
+        <f>MAX(0,N84)*$D$58</f>
         <v/>
       </c>
     </row>
@@ -4986,48 +5070,88 @@
           <t>EBITDA - Taxes</t>
         </is>
       </c>
-      <c r="E86" s="7">
-        <f>E70-E75</f>
-        <v/>
-      </c>
-      <c r="F86" s="7">
-        <f>F70-F75</f>
-        <v/>
+      <c r="E86" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="G86" s="7">
-        <f>G70-G75</f>
+        <f>G80-G85</f>
         <v/>
       </c>
       <c r="H86" s="7">
-        <f>H70-H75</f>
+        <f>H80-H85</f>
         <v/>
       </c>
       <c r="I86" s="7">
-        <f>I70-I75</f>
+        <f>I80-I85</f>
         <v/>
       </c>
       <c r="J86" s="7">
-        <f>J70-J75</f>
+        <f>J80-J85</f>
         <v/>
       </c>
       <c r="K86" s="7">
-        <f>K70-K75</f>
+        <f>K80-K85</f>
         <v/>
       </c>
       <c r="L86" s="7">
-        <f>L70-L75</f>
+        <f>L80-L85</f>
         <v/>
       </c>
       <c r="M86" s="7">
-        <f>M70-M75</f>
+        <f>M80-M85</f>
         <v/>
       </c>
       <c r="N86" s="7">
-        <f>N70-N75</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87"/>
+        <f>N80-N85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <f>$D$64</f>
+        <v/>
+      </c>
+      <c r="H87">
+        <f>G92</f>
+        <v/>
+      </c>
+      <c r="I87">
+        <f>H92</f>
+        <v/>
+      </c>
+      <c r="J87">
+        <f>I92</f>
+        <v/>
+      </c>
+      <c r="K87">
+        <f>J92</f>
+        <v/>
+      </c>
+      <c r="L87">
+        <f>K92</f>
+        <v/>
+      </c>
+      <c r="M87">
+        <f>L92</f>
+        <v/>
+      </c>
+      <c r="N87">
+        <f>M92</f>
+        <v/>
+      </c>
+    </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
@@ -5037,16 +5161,44 @@
       <c r="B88" s="4" t="n"/>
       <c r="C88" s="4" t="n"/>
       <c r="D88" s="4" t="n"/>
-      <c r="E88" s="4" t="n"/>
-      <c r="F88" s="4" t="n"/>
-      <c r="G88" s="4" t="n"/>
-      <c r="H88" s="4" t="n"/>
-      <c r="I88" s="4" t="n"/>
-      <c r="J88" s="4" t="n"/>
-      <c r="K88" s="4" t="n"/>
-      <c r="L88" s="4" t="n"/>
-      <c r="M88" s="4" t="n"/>
-      <c r="N88" s="4" t="n"/>
+      <c r="E88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="4">
+        <f>G87*$D$48</f>
+        <v/>
+      </c>
+      <c r="H88" s="4">
+        <f>H87*$D$48</f>
+        <v/>
+      </c>
+      <c r="I88" s="4">
+        <f>I87*$D$48</f>
+        <v/>
+      </c>
+      <c r="J88" s="4">
+        <f>J87*$D$48</f>
+        <v/>
+      </c>
+      <c r="K88" s="4">
+        <f>K87*$D$48</f>
+        <v/>
+      </c>
+      <c r="L88" s="4">
+        <f>L87*$D$48</f>
+        <v/>
+      </c>
+      <c r="M88" s="4">
+        <f>M87*$D$48</f>
+        <v/>
+      </c>
+      <c r="N88" s="4">
+        <f>N87*$D$48</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -5060,44 +5212,45 @@
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr"/>
-      <c r="E89" s="15">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F89" s="15">
-        <f>0</f>
-        <v/>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="G89" s="15">
-        <f>$D$54</f>
+        <f>$D$64</f>
         <v/>
       </c>
       <c r="H89" s="15">
-        <f>G84</f>
+        <f>G94</f>
         <v/>
       </c>
       <c r="I89" s="15">
-        <f>H84</f>
+        <f>H94</f>
         <v/>
       </c>
       <c r="J89" s="15">
-        <f>I84</f>
+        <f>I94</f>
         <v/>
       </c>
       <c r="K89" s="15">
-        <f>J84</f>
+        <f>J94</f>
         <v/>
       </c>
       <c r="L89" s="15">
-        <f>K84</f>
+        <f>K94</f>
         <v/>
       </c>
       <c r="M89" s="15">
-        <f>L84</f>
+        <f>L94</f>
         <v/>
       </c>
       <c r="N89" s="15">
-        <f>M84</f>
+        <f>M94</f>
         <v/>
       </c>
     </row>
@@ -5117,44 +5270,42 @@
           <t>Beg Bal × Int Rate</t>
         </is>
       </c>
-      <c r="E90" s="15">
-        <f>E79*$D$38</f>
-        <v/>
-      </c>
-      <c r="F90" s="15">
-        <f>F79*$D$38</f>
-        <v/>
+      <c r="E90" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="G90" s="15">
-        <f>G79*$D$38</f>
+        <f>G89*$D$48</f>
         <v/>
       </c>
       <c r="H90" s="15">
-        <f>H79*$D$38</f>
+        <f>H89*$D$48</f>
         <v/>
       </c>
       <c r="I90" s="15">
-        <f>I79*$D$38</f>
+        <f>I89*$D$48</f>
         <v/>
       </c>
       <c r="J90" s="15">
-        <f>J79*$D$38</f>
+        <f>J89*$D$48</f>
         <v/>
       </c>
       <c r="K90" s="15">
-        <f>K79*$D$38</f>
+        <f>K89*$D$48</f>
         <v/>
       </c>
       <c r="L90" s="15">
-        <f>L79*$D$38</f>
+        <f>L89*$D$48</f>
         <v/>
       </c>
       <c r="M90" s="15">
-        <f>M79*$D$38</f>
+        <f>M89*$D$48</f>
         <v/>
       </c>
       <c r="N90" s="15">
-        <f>N79*$D$38</f>
+        <f>N89*$D$48</f>
         <v/>
       </c>
     </row>
@@ -5174,44 +5325,42 @@
           <t>CFADS / Target DSCR</t>
         </is>
       </c>
-      <c r="E91" s="15">
-        <f>IF(E76&gt;0,E76/$D$40,0)</f>
-        <v/>
-      </c>
-      <c r="F91" s="15">
-        <f>IF(F76&gt;0,F76/$D$40,0)</f>
-        <v/>
+      <c r="E91" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="G91" s="15">
-        <f>IF(G76&gt;0,G76/$D$40,0)</f>
+        <f>G86/$D$50</f>
         <v/>
       </c>
       <c r="H91" s="15">
-        <f>IF(H76&gt;0,H76/$D$40,0)</f>
+        <f>H86/$D$50</f>
         <v/>
       </c>
       <c r="I91" s="15">
-        <f>IF(I76&gt;0,I76/$D$40,0)</f>
+        <f>I86/$D$50</f>
         <v/>
       </c>
       <c r="J91" s="15">
-        <f>IF(J76&gt;0,J76/$D$40,0)</f>
+        <f>J86/$D$50</f>
         <v/>
       </c>
       <c r="K91" s="15">
-        <f>IF(K76&gt;0,K76/$D$40,0)</f>
+        <f>K86/$D$50</f>
         <v/>
       </c>
       <c r="L91" s="15">
-        <f>IF(L76&gt;0,L76/$D$40,0)</f>
+        <f>L86/$D$50</f>
         <v/>
       </c>
       <c r="M91" s="15">
-        <f>IF(M76&gt;0,M76/$D$40,0)</f>
+        <f>M86/$D$50</f>
         <v/>
       </c>
       <c r="N91" s="15">
-        <f>IF(N76&gt;0,N76/$D$40,0)</f>
+        <f>N86/$D$50</f>
         <v/>
       </c>
     </row>
@@ -5231,44 +5380,42 @@
           <t>Target DS - Interest</t>
         </is>
       </c>
-      <c r="E92" s="15">
-        <f>MIN(MAX(0,E81-E80),E79)</f>
-        <v/>
-      </c>
-      <c r="F92" s="15">
-        <f>MIN(MAX(0,F81-F80),F79)</f>
-        <v/>
+      <c r="E92" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="G92" s="15">
-        <f>MIN(MAX(0,G81-G80),G79)</f>
+        <f>MIN(MAX(0,G91-G90),G89)</f>
         <v/>
       </c>
       <c r="H92" s="15">
-        <f>MIN(MAX(0,H81-H80),H79)</f>
+        <f>MIN(MAX(0,H91-H90),H89)</f>
         <v/>
       </c>
       <c r="I92" s="15">
-        <f>MIN(MAX(0,I81-I80),I79)</f>
+        <f>MIN(MAX(0,I91-I90),I89)</f>
         <v/>
       </c>
       <c r="J92" s="15">
-        <f>MIN(MAX(0,J81-J80),J79)</f>
+        <f>MIN(MAX(0,J91-J90),J89)</f>
         <v/>
       </c>
       <c r="K92" s="15">
-        <f>MIN(MAX(0,K81-K80),K79)</f>
+        <f>MIN(MAX(0,K91-K90),K89)</f>
         <v/>
       </c>
       <c r="L92" s="15">
-        <f>MIN(MAX(0,L81-L80),L79)</f>
+        <f>MIN(MAX(0,L91-L90),L89)</f>
         <v/>
       </c>
       <c r="M92" s="15">
-        <f>MIN(MAX(0,M81-M80),M79)</f>
+        <f>MIN(MAX(0,M91-M90),M89)</f>
         <v/>
       </c>
       <c r="N92" s="15">
-        <f>MIN(MAX(0,N81-N80),N79)</f>
+        <f>MIN(MAX(0,N91-N90),N89)</f>
         <v/>
       </c>
     </row>
@@ -5288,44 +5435,42 @@
           <t>Interest + Principal</t>
         </is>
       </c>
-      <c r="E93" s="15">
-        <f>E80+E82</f>
-        <v/>
-      </c>
-      <c r="F93" s="15">
-        <f>F80+F82</f>
-        <v/>
-      </c>
-      <c r="G93" s="15">
-        <f>G80+G82</f>
-        <v/>
-      </c>
-      <c r="H93" s="15">
-        <f>H80+H82</f>
-        <v/>
-      </c>
-      <c r="I93" s="15">
-        <f>I80+I82</f>
-        <v/>
-      </c>
-      <c r="J93" s="15">
-        <f>J80+J82</f>
-        <v/>
-      </c>
-      <c r="K93" s="15">
-        <f>K80+K82</f>
-        <v/>
-      </c>
-      <c r="L93" s="15">
-        <f>L80+L82</f>
-        <v/>
-      </c>
-      <c r="M93" s="15">
-        <f>M80+M82</f>
-        <v/>
-      </c>
-      <c r="N93" s="15">
-        <f>N80+N82</f>
+      <c r="E93" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="51">
+        <f>G90+G92</f>
+        <v/>
+      </c>
+      <c r="H93" s="51">
+        <f>H90+H92</f>
+        <v/>
+      </c>
+      <c r="I93" s="51">
+        <f>I90+I92</f>
+        <v/>
+      </c>
+      <c r="J93" s="51">
+        <f>J90+J92</f>
+        <v/>
+      </c>
+      <c r="K93" s="51">
+        <f>K90+K92</f>
+        <v/>
+      </c>
+      <c r="L93" s="51">
+        <f>L90+L92</f>
+        <v/>
+      </c>
+      <c r="M93" s="51">
+        <f>M90+M92</f>
+        <v/>
+      </c>
+      <c r="N93" s="51">
+        <f>N90+N92</f>
         <v/>
       </c>
     </row>
@@ -5345,44 +5490,42 @@
           <t>Beg - Principal</t>
         </is>
       </c>
-      <c r="E94" s="15">
-        <f>MAX(0,E79-E82)</f>
-        <v/>
-      </c>
-      <c r="F94" s="15">
-        <f>MAX(0,F79-F82)</f>
-        <v/>
+      <c r="E94" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="G94" s="15">
-        <f>MAX(0,G79-G82)</f>
+        <f>MAX(0,G89-G92)</f>
         <v/>
       </c>
       <c r="H94" s="15">
-        <f>MAX(0,H79-H82)</f>
+        <f>MAX(0,H89-H92)</f>
         <v/>
       </c>
       <c r="I94" s="15">
-        <f>MAX(0,I79-I82)</f>
+        <f>MAX(0,I89-I92)</f>
         <v/>
       </c>
       <c r="J94" s="15">
-        <f>MAX(0,J79-J82)</f>
+        <f>MAX(0,J89-J92)</f>
         <v/>
       </c>
       <c r="K94" s="15">
-        <f>MAX(0,K79-K82)</f>
+        <f>MAX(0,K89-K92)</f>
         <v/>
       </c>
       <c r="L94" s="15">
-        <f>MAX(0,L79-L82)</f>
+        <f>MAX(0,L89-L92)</f>
         <v/>
       </c>
       <c r="M94" s="15">
-        <f>MAX(0,M79-M82)</f>
+        <f>MAX(0,M89-M92)</f>
         <v/>
       </c>
       <c r="N94" s="15">
-        <f>MAX(0,N79-N82)</f>
+        <f>MAX(0,N89-N92)</f>
         <v/>
       </c>
     </row>
@@ -5402,48 +5545,45 @@
           <t>CFADS / Actual DS</t>
         </is>
       </c>
-      <c r="E95" s="19">
-        <f>IF(E83&gt;0,E76/E83,0)</f>
-        <v/>
-      </c>
-      <c r="F95" s="19">
-        <f>IF(F83&gt;0,F76/F83,0)</f>
-        <v/>
+      <c r="E95" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="19" t="n">
+        <v>0</v>
       </c>
       <c r="G95" s="19">
-        <f>IF(G83&gt;0,G76/G83,0)</f>
+        <f>IF(G93&gt;0,G86/G93,0)</f>
         <v/>
       </c>
       <c r="H95" s="19">
-        <f>IF(H83&gt;0,H76/H83,0)</f>
+        <f>IF(H93&gt;0,H86/H93,0)</f>
         <v/>
       </c>
       <c r="I95" s="19">
-        <f>IF(I83&gt;0,I76/I83,0)</f>
+        <f>IF(I93&gt;0,I86/I93,0)</f>
         <v/>
       </c>
       <c r="J95" s="19">
-        <f>IF(J83&gt;0,J76/J83,0)</f>
+        <f>IF(J93&gt;0,J86/J93,0)</f>
         <v/>
       </c>
       <c r="K95" s="19">
-        <f>IF(K83&gt;0,K76/K83,0)</f>
+        <f>IF(K93&gt;0,K86/K93,0)</f>
         <v/>
       </c>
       <c r="L95" s="19">
-        <f>IF(L83&gt;0,L76/L83,0)</f>
+        <f>IF(L93&gt;0,L86/L93,0)</f>
         <v/>
       </c>
       <c r="M95" s="19">
-        <f>IF(M83&gt;0,M76/M83,0)</f>
+        <f>IF(M93&gt;0,M86/M93,0)</f>
         <v/>
       </c>
       <c r="N95" s="19">
-        <f>IF(N83&gt;0,N76/N83,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96"/>
+        <f>IF(N93&gt;0,N86/N93,0)</f>
+        <v/>
+      </c>
+    </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
@@ -5453,16 +5593,43 @@
       <c r="B97" s="4" t="n"/>
       <c r="C97" s="4" t="n"/>
       <c r="D97" s="4" t="n"/>
-      <c r="E97" s="4" t="n"/>
-      <c r="F97" s="4" t="n"/>
-      <c r="G97" s="4" t="n"/>
-      <c r="H97" s="4" t="n"/>
-      <c r="I97" s="4" t="n"/>
-      <c r="J97" s="4" t="n"/>
-      <c r="K97" s="4" t="n"/>
-      <c r="L97" s="4" t="n"/>
-      <c r="M97" s="4" t="n"/>
-      <c r="N97" s="4" t="n"/>
+      <c r="E97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="4">
+        <f>H91*$D$49/12</f>
+        <v/>
+      </c>
+      <c r="H97" s="4">
+        <f>I91*$D$49/12</f>
+        <v/>
+      </c>
+      <c r="I97" s="4">
+        <f>J91*$D$49/12</f>
+        <v/>
+      </c>
+      <c r="J97" s="4">
+        <f>K91*$D$49/12</f>
+        <v/>
+      </c>
+      <c r="K97" s="4">
+        <f>L91*$D$49/12</f>
+        <v/>
+      </c>
+      <c r="L97" s="4">
+        <f>M91*$D$49/12</f>
+        <v/>
+      </c>
+      <c r="M97" s="4">
+        <f>N91*$D$49/12</f>
+        <v/>
+      </c>
+      <c r="N97" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
@@ -5480,49 +5647,45 @@
           <t>Next Yr DS × DSRA Months / 12</t>
         </is>
       </c>
-      <c r="D98" s="15">
-        <f>G83*$D$39/12</f>
-        <v/>
-      </c>
-      <c r="E98" s="15">
-        <f>G83*$D$39/12</f>
-        <v/>
-      </c>
-      <c r="F98" s="15">
-        <f>G83*$D$39/12</f>
-        <v/>
+      <c r="D98" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="G98" s="15">
-        <f>H83*$D$39/12</f>
+        <f>H93*$D$49/12</f>
         <v/>
       </c>
       <c r="H98" s="15">
-        <f>I83*$D$39/12</f>
+        <f>I93*$D$49/12</f>
         <v/>
       </c>
       <c r="I98" s="15">
-        <f>J83*$D$39/12</f>
+        <f>J93*$D$49/12</f>
         <v/>
       </c>
       <c r="J98" s="15">
-        <f>K83*$D$39/12</f>
+        <f>K93*$D$49/12</f>
         <v/>
       </c>
       <c r="K98" s="15">
-        <f>L83*$D$39/12</f>
+        <f>L93*$D$49/12</f>
         <v/>
       </c>
       <c r="L98" s="15">
-        <f>M83*$D$39/12</f>
+        <f>M93*$D$49/12</f>
         <v/>
       </c>
       <c r="M98" s="15">
-        <f>N83*$D$39/12</f>
-        <v/>
-      </c>
-      <c r="N98" s="15">
-        <f>0</f>
-        <v/>
+        <f>N93*$D$49/12</f>
+        <v/>
+      </c>
+      <c r="N98" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -5537,48 +5700,45 @@
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr"/>
-      <c r="D99" s="15">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E99" s="15">
-        <f>D91</f>
-        <v/>
-      </c>
-      <c r="F99" s="15">
-        <f>E91</f>
-        <v/>
+      <c r="D99" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="G99" s="15">
-        <f>F91</f>
+        <f>D114</f>
         <v/>
       </c>
       <c r="H99" s="15">
-        <f>G91</f>
+        <f>G101</f>
         <v/>
       </c>
       <c r="I99" s="15">
-        <f>H91</f>
+        <f>H101</f>
         <v/>
       </c>
       <c r="J99" s="15">
-        <f>I91</f>
+        <f>I101</f>
         <v/>
       </c>
       <c r="K99" s="15">
-        <f>J91</f>
+        <f>J101</f>
         <v/>
       </c>
       <c r="L99" s="15">
-        <f>K91</f>
+        <f>K101</f>
         <v/>
       </c>
       <c r="M99" s="15">
-        <f>L91</f>
+        <f>L101</f>
         <v/>
       </c>
       <c r="N99" s="15">
-        <f>M91</f>
+        <f>M101</f>
         <v/>
       </c>
     </row>
@@ -5602,44 +5762,42 @@
         <f>D88-D89</f>
         <v/>
       </c>
-      <c r="E100" s="15">
-        <f>E88-E89</f>
-        <v/>
-      </c>
-      <c r="F100" s="15">
-        <f>F88-F89</f>
-        <v/>
+      <c r="E100" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="G100" s="15">
-        <f>G88-G89</f>
+        <f>G98-G99</f>
         <v/>
       </c>
       <c r="H100" s="15">
-        <f>H88-H89</f>
+        <f>H98-H99</f>
         <v/>
       </c>
       <c r="I100" s="15">
-        <f>I88-I89</f>
+        <f>I98-I99</f>
         <v/>
       </c>
       <c r="J100" s="15">
-        <f>J88-J89</f>
+        <f>J98-J99</f>
         <v/>
       </c>
       <c r="K100" s="15">
-        <f>K88-K89</f>
+        <f>K98-K99</f>
         <v/>
       </c>
       <c r="L100" s="15">
-        <f>L88-L89</f>
+        <f>L98-L99</f>
         <v/>
       </c>
       <c r="M100" s="15">
-        <f>M88-M89</f>
+        <f>M98-M99</f>
         <v/>
       </c>
       <c r="N100" s="15">
-        <f>N88-N89</f>
+        <f>N98-N99</f>
         <v/>
       </c>
     </row>
@@ -5663,48 +5821,45 @@
         <f>D89+D90</f>
         <v/>
       </c>
-      <c r="E101" s="15">
-        <f>E89+E90</f>
-        <v/>
-      </c>
-      <c r="F101" s="15">
-        <f>F89+F90</f>
-        <v/>
+      <c r="E101" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="G101" s="15">
-        <f>G89+G90</f>
+        <f>G99+G100</f>
         <v/>
       </c>
       <c r="H101" s="15">
-        <f>H89+H90</f>
+        <f>H99+H100</f>
         <v/>
       </c>
       <c r="I101" s="15">
-        <f>I89+I90</f>
+        <f>I99+I100</f>
         <v/>
       </c>
       <c r="J101" s="15">
-        <f>J89+J90</f>
+        <f>J99+J100</f>
         <v/>
       </c>
       <c r="K101" s="15">
-        <f>K89+K90</f>
+        <f>K99+K100</f>
         <v/>
       </c>
       <c r="L101" s="15">
-        <f>L89+L90</f>
+        <f>L99+L100</f>
         <v/>
       </c>
       <c r="M101" s="15">
-        <f>M89+M90</f>
+        <f>M99+M100</f>
         <v/>
       </c>
       <c r="N101" s="15">
-        <f>N89+N90</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102"/>
+        <f>N99+N100</f>
+        <v/>
+      </c>
+    </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
@@ -5714,16 +5869,44 @@
       <c r="B103" s="4" t="n"/>
       <c r="C103" s="4" t="n"/>
       <c r="D103" s="4" t="n"/>
-      <c r="E103" s="4" t="n"/>
-      <c r="F103" s="4" t="n"/>
-      <c r="G103" s="4" t="n"/>
-      <c r="H103" s="4" t="n"/>
-      <c r="I103" s="4" t="n"/>
-      <c r="J103" s="4" t="n"/>
-      <c r="K103" s="4" t="n"/>
-      <c r="L103" s="4" t="n"/>
-      <c r="M103" s="4" t="n"/>
-      <c r="N103" s="4" t="n"/>
+      <c r="E103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="4">
+        <f>G83-G91-G99</f>
+        <v/>
+      </c>
+      <c r="H103" s="4">
+        <f>H83-H91-H99</f>
+        <v/>
+      </c>
+      <c r="I103" s="4">
+        <f>I83-I91-I99</f>
+        <v/>
+      </c>
+      <c r="J103" s="4">
+        <f>J83-J91-J99</f>
+        <v/>
+      </c>
+      <c r="K103" s="4">
+        <f>K83-K91-K99</f>
+        <v/>
+      </c>
+      <c r="L103" s="4">
+        <f>L83-L91-L99</f>
+        <v/>
+      </c>
+      <c r="M103" s="4">
+        <f>M83-M91-M99</f>
+        <v/>
+      </c>
+      <c r="N103" s="4">
+        <f>N83-N91-N99</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -5741,44 +5924,42 @@
           <t>CFADS - DS - DSRA Fund</t>
         </is>
       </c>
-      <c r="E104" s="15">
-        <f>E76-E83-E90</f>
-        <v/>
-      </c>
-      <c r="F104" s="15">
-        <f>F76-F83-F90</f>
-        <v/>
+      <c r="E104" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="G104" s="15">
-        <f>G76-G83-G90</f>
+        <f>G86-G93-G100</f>
         <v/>
       </c>
       <c r="H104" s="15">
-        <f>H76-H83-H90</f>
+        <f>H86-H93-H100</f>
         <v/>
       </c>
       <c r="I104" s="15">
-        <f>I76-I83-I90</f>
+        <f>I86-I93-I100</f>
         <v/>
       </c>
       <c r="J104" s="15">
-        <f>J76-J83-J90</f>
+        <f>J86-J93-J100</f>
         <v/>
       </c>
       <c r="K104" s="15">
-        <f>K76-K83-K90</f>
+        <f>K86-K93-K100</f>
         <v/>
       </c>
       <c r="L104" s="15">
-        <f>L76-L83-L90</f>
+        <f>L86-L93-L100</f>
         <v/>
       </c>
       <c r="M104" s="15">
-        <f>M76-M83-M90</f>
+        <f>M86-M93-M100</f>
         <v/>
       </c>
       <c r="N104" s="15">
-        <f>N76-N83-N90</f>
+        <f>N86-N93-N100</f>
         <v/>
       </c>
     </row>
@@ -5794,44 +5975,46 @@
           <t>PASS if DSCR ≥ Lock-up</t>
         </is>
       </c>
-      <c r="E105" s="17">
-        <f>IF(E85&gt;=$D$41,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="F105" s="17">
-        <f>IF(F85&gt;=$D$41,"PASS","LOCKED")</f>
-        <v/>
+      <c r="E105" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F105" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="G105" s="17">
-        <f>IF(G85&gt;=$D$41,"PASS","LOCKED")</f>
+        <f>IF(G95&gt;=$D$51,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="H105" s="17">
-        <f>IF(H85&gt;=$D$41,"PASS","LOCKED")</f>
+        <f>IF(H95&gt;=$D$51,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="I105" s="17">
-        <f>IF(I85&gt;=$D$41,"PASS","LOCKED")</f>
+        <f>IF(I95&gt;=$D$51,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="J105" s="17">
-        <f>IF(J85&gt;=$D$41,"PASS","LOCKED")</f>
+        <f>IF(J95&gt;=$D$51,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="K105" s="17">
-        <f>IF(K85&gt;=$D$41,"PASS","LOCKED")</f>
+        <f>IF(K95&gt;=$D$51,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="L105" s="17">
-        <f>IF(L85&gt;=$D$41,"PASS","LOCKED")</f>
+        <f>IF(L95&gt;=$D$51,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="M105" s="17">
-        <f>IF(M85&gt;=$D$41,"PASS","LOCKED")</f>
+        <f>IF(M95&gt;=$D$51,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="N105" s="17">
-        <f>IF(N85&gt;=$D$41,"PASS","LOCKED")</f>
+        <f>IF(N95&gt;=$D$51,"PASS","LOCKED")</f>
         <v/>
       </c>
     </row>
@@ -5851,48 +6034,45 @@
           <t>If PASS, MAX(0, Cash Avail)</t>
         </is>
       </c>
-      <c r="E106" s="7">
-        <f>IF(E95="PASS",MAX(0,E94),0)</f>
-        <v/>
-      </c>
-      <c r="F106" s="7">
-        <f>IF(F95="PASS",MAX(0,F94),0)</f>
-        <v/>
+      <c r="E106" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="G106" s="7">
-        <f>IF(G95="PASS",MAX(0,G94),0)</f>
+        <f>IF(G105="PASS",MAX(0,G104),0)</f>
         <v/>
       </c>
       <c r="H106" s="7">
-        <f>IF(H95="PASS",MAX(0,H94),0)</f>
+        <f>IF(H105="PASS",MAX(0,H104),0)</f>
         <v/>
       </c>
       <c r="I106" s="7">
-        <f>IF(I95="PASS",MAX(0,I94),0)</f>
+        <f>IF(I105="PASS",MAX(0,I104),0)</f>
         <v/>
       </c>
       <c r="J106" s="7">
-        <f>IF(J95="PASS",MAX(0,J94),0)</f>
+        <f>IF(J105="PASS",MAX(0,J104),0)</f>
         <v/>
       </c>
       <c r="K106" s="7">
-        <f>IF(K95="PASS",MAX(0,K94),0)</f>
+        <f>IF(K105="PASS",MAX(0,K104),0)</f>
         <v/>
       </c>
       <c r="L106" s="7">
-        <f>IF(L95="PASS",MAX(0,L94),0)</f>
+        <f>IF(L105="PASS",MAX(0,L104),0)</f>
         <v/>
       </c>
       <c r="M106" s="7">
-        <f>IF(M95="PASS",MAX(0,M94),0)</f>
+        <f>IF(M105="PASS",MAX(0,M104),0)</f>
         <v/>
       </c>
       <c r="N106" s="7">
-        <f>IF(N95="PASS",MAX(0,N94),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107"/>
+        <f>IF(N105="PASS",MAX(0,N104),0)</f>
+        <v/>
+      </c>
+    </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
@@ -5921,6 +6101,10 @@
       </c>
       <c r="B109" s="6" t="inlineStr"/>
       <c r="C109" s="6" t="inlineStr"/>
+      <c r="D109">
+        <f>$D$27+$D$28+$D$29+$D$62</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
@@ -5935,7 +6119,7 @@
       </c>
       <c r="C110" s="6" t="inlineStr"/>
       <c r="D110" s="15">
-        <f>$D$17</f>
+        <f>$D$27</f>
         <v/>
       </c>
     </row>
@@ -5952,7 +6136,7 @@
       </c>
       <c r="C111" s="6" t="inlineStr"/>
       <c r="D111" s="15">
-        <f>$D$18</f>
+        <f>$D$28</f>
         <v/>
       </c>
     </row>
@@ -5969,7 +6153,7 @@
       </c>
       <c r="C112" s="6" t="inlineStr"/>
       <c r="D112" s="15">
-        <f>$D$19</f>
+        <f>$D$29</f>
         <v/>
       </c>
     </row>
@@ -5986,7 +6170,7 @@
       </c>
       <c r="C113" s="6" t="inlineStr"/>
       <c r="D113" s="15">
-        <f>$D$52</f>
+        <f>$D$62</f>
         <v/>
       </c>
     </row>
@@ -6003,7 +6187,7 @@
       </c>
       <c r="C114" s="6" t="inlineStr"/>
       <c r="D114" s="15">
-        <f>G88</f>
+        <f>G98</f>
         <v/>
       </c>
     </row>
@@ -6020,11 +6204,10 @@
       </c>
       <c r="C115" s="6" t="inlineStr"/>
       <c r="D115" s="7">
-        <f>SUM(D100:D104)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="116"/>
+        <f>D110+D111+D112+D113+D114</f>
+        <v/>
+      </c>
+    </row>
     <row r="117">
       <c r="A117" s="18" t="inlineStr">
         <is>
@@ -6033,6 +6216,10 @@
       </c>
       <c r="B117" s="6" t="inlineStr"/>
       <c r="C117" s="6" t="inlineStr"/>
+      <c r="D117">
+        <f>IF(ABS(D111-D115)&lt;0.01,"PASS","FAIL")</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
@@ -6047,7 +6234,7 @@
       </c>
       <c r="C118" s="6" t="inlineStr"/>
       <c r="D118" s="15">
-        <f>$D$51</f>
+        <f>$D$61</f>
         <v/>
       </c>
     </row>
@@ -6064,7 +6251,7 @@
       </c>
       <c r="C119" s="6" t="inlineStr"/>
       <c r="D119" s="15">
-        <f>$D$54</f>
+        <f>$D$64</f>
         <v/>
       </c>
     </row>
@@ -6081,7 +6268,7 @@
       </c>
       <c r="C120" s="6" t="inlineStr"/>
       <c r="D120" s="15">
-        <f>D62</f>
+        <f>D115-D118-D119+D118</f>
         <v/>
       </c>
     </row>
@@ -6098,7 +6285,7 @@
       </c>
       <c r="C121" s="6" t="inlineStr"/>
       <c r="D121" s="7">
-        <f>D109+D110</f>
+        <f>D119+D120</f>
         <v/>
       </c>
     </row>
@@ -6111,11 +6298,16 @@
       <c r="B122" s="6" t="inlineStr"/>
       <c r="C122" s="6" t="inlineStr"/>
       <c r="D122" s="10">
-        <f>IF(ABS(D105-D111)&lt;0.01,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="123"/>
+        <f>IF(ABS(D115-D121)&lt;0.01,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="D123">
+        <f>N100</f>
+        <v/>
+      </c>
+    </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
@@ -6124,7 +6316,10 @@
       </c>
       <c r="B124" s="4" t="n"/>
       <c r="C124" s="4" t="n"/>
-      <c r="D124" s="4" t="n"/>
+      <c r="D124" s="4">
+        <f>D121-D122+D123</f>
+        <v/>
+      </c>
       <c r="E124" s="4" t="n"/>
       <c r="F124" s="4" t="n"/>
       <c r="G124" s="4" t="n"/>
@@ -6152,6 +6347,10 @@
           <t>Dep × Operating Years</t>
         </is>
       </c>
+      <c r="D125">
+        <f>$D$65*(10-3+1)</f>
+        <v/>
+      </c>
       <c r="N125" s="15">
         <f>$D$55*8</f>
         <v/>
@@ -6173,6 +6372,10 @@
           <t>RAB at COD - Cum Dep</t>
         </is>
       </c>
+      <c r="D126">
+        <f>$D$63-D125</f>
+        <v/>
+      </c>
       <c r="N126" s="15">
         <f>$D$53-N115</f>
         <v/>
@@ -6194,8 +6397,48 @@
           <t>Exit RAB × xRAB Multiple</t>
         </is>
       </c>
+      <c r="D127">
+        <f>D126*$D$54</f>
+        <v/>
+      </c>
+      <c r="E127">
+        <f>-E69</f>
+        <v/>
+      </c>
+      <c r="F127">
+        <f>-F70</f>
+        <v/>
+      </c>
+      <c r="G127">
+        <f>-G71+G105</f>
+        <v/>
+      </c>
+      <c r="H127">
+        <f>H105</f>
+        <v/>
+      </c>
+      <c r="I127">
+        <f>I105</f>
+        <v/>
+      </c>
+      <c r="J127">
+        <f>J105</f>
+        <v/>
+      </c>
+      <c r="K127">
+        <f>K105</f>
+        <v/>
+      </c>
+      <c r="L127">
+        <f>L105</f>
+        <v/>
+      </c>
+      <c r="M127">
+        <f>M105</f>
+        <v/>
+      </c>
       <c r="N127" s="15">
-        <f>N116*$D$44</f>
+        <f>N105+D124</f>
         <v/>
       </c>
     </row>
@@ -6215,6 +6458,10 @@
           <t>Ending Bal at Exit</t>
         </is>
       </c>
+      <c r="D128" s="52">
+        <f>N94</f>
+        <v/>
+      </c>
       <c r="N128" s="15">
         <f>N84</f>
         <v/>
@@ -6236,6 +6483,10 @@
           <t>DSRA Ending at Exit</t>
         </is>
       </c>
+      <c r="D129" s="53">
+        <f>N101</f>
+        <v/>
+      </c>
       <c r="N129" s="15">
         <f>N91</f>
         <v/>
@@ -6257,12 +6508,15 @@
           <t>Exit EV - Debt + DSRA</t>
         </is>
       </c>
+      <c r="D130">
+        <f>D127-D128+D129</f>
+        <v/>
+      </c>
       <c r="N130" s="7">
         <f>N117-N118+N119</f>
         <v/>
       </c>
     </row>
-    <row r="131"/>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
@@ -6296,47 +6550,47 @@
       </c>
       <c r="C133" s="6" t="inlineStr"/>
       <c r="D133" s="15">
-        <f>-D58</f>
+        <f>-D68</f>
         <v/>
       </c>
       <c r="E133" s="15">
-        <f>-E59</f>
+        <f>-E69</f>
         <v/>
       </c>
       <c r="F133" s="15">
-        <f>-F60</f>
+        <f>-F70</f>
         <v/>
       </c>
       <c r="G133" s="15">
-        <f>-G61-G90+G96</f>
+        <f>-G71+G106</f>
         <v/>
       </c>
       <c r="H133" s="15">
-        <f>H96</f>
+        <f>H106</f>
         <v/>
       </c>
       <c r="I133" s="15">
-        <f>I96</f>
+        <f>I106</f>
         <v/>
       </c>
       <c r="J133" s="15">
-        <f>J96</f>
+        <f>J106</f>
         <v/>
       </c>
       <c r="K133" s="15">
-        <f>K96</f>
+        <f>K106</f>
         <v/>
       </c>
       <c r="L133" s="15">
-        <f>L96</f>
+        <f>L106</f>
         <v/>
       </c>
       <c r="M133" s="15">
-        <f>M96</f>
+        <f>M106</f>
         <v/>
       </c>
       <c r="N133" s="15">
-        <f>N96+N120</f>
+        <f>N106+D130</f>
         <v/>
       </c>
     </row>
@@ -6357,7 +6611,7 @@
         </is>
       </c>
       <c r="D134" s="20">
-        <f>IRR(D123:N123)</f>
+        <f>IRR(D133:N133)</f>
         <v/>
       </c>
     </row>
@@ -6378,11 +6632,10 @@
         </is>
       </c>
       <c r="D135" s="19">
-        <f>SUMIF(D123:N123,"&gt;0")/-SUMIF(D123:N123,"&lt;0")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="136"/>
+        <f>(SUM(G133:N133))/(D68+E69+F70+G71)</f>
+        <v/>
+      </c>
+    </row>
     <row r="137">
       <c r="A137" s="18" t="inlineStr">
         <is>
@@ -6405,47 +6658,45 @@
       </c>
       <c r="C138" s="6" t="inlineStr"/>
       <c r="D138" s="15">
-        <f>-$D$17</f>
-        <v/>
-      </c>
-      <c r="E138" s="15">
-        <f>-$D$18</f>
-        <v/>
-      </c>
-      <c r="F138" s="15">
-        <f>-$D$19</f>
-        <v/>
+        <f>-$D$63</f>
+        <v/>
+      </c>
+      <c r="E138" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="G138" s="15">
-        <f>G76</f>
+        <f>G86</f>
         <v/>
       </c>
       <c r="H138" s="15">
-        <f>H76</f>
+        <f>H86</f>
         <v/>
       </c>
       <c r="I138" s="15">
-        <f>I76</f>
+        <f>I86</f>
         <v/>
       </c>
       <c r="J138" s="15">
-        <f>J76</f>
+        <f>J86</f>
         <v/>
       </c>
       <c r="K138" s="15">
-        <f>K76</f>
+        <f>K86</f>
         <v/>
       </c>
       <c r="L138" s="15">
-        <f>L76</f>
+        <f>L86</f>
         <v/>
       </c>
       <c r="M138" s="15">
-        <f>M76</f>
+        <f>M86</f>
         <v/>
       </c>
       <c r="N138" s="15">
-        <f>N76+N117</f>
+        <f>N86+D127</f>
         <v/>
       </c>
     </row>
@@ -6466,7 +6717,7 @@
         </is>
       </c>
       <c r="D139" s="20">
-        <f>IRR(D128:N128)</f>
+        <f>IRR(D138:N138)</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Model_4_Transmission.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_4_Transmission.xlsx
@@ -3722,7 +3722,7 @@
       <c r="B22" s="6" t="inlineStr"/>
       <c r="C22" s="6" t="inlineStr"/>
       <c r="D22" s="10">
-        <f>IF(N84&lt;1,"PASS","FAIL")</f>
+        <f>IF(N94&lt;1,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Model_4_Transmission.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_4_Transmission.xlsx
@@ -3708,10 +3708,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr"/>
       <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="10">
-        <f>D112</f>
-        <v/>
-      </c>
+      <c r="D21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -3739,7 +3736,7 @@
         </is>
       </c>
       <c r="D23" s="10">
-        <f>IF(D6&gt;=1.35,"PASS","FAIL")</f>
+        <f>IF(MINIFS(G95:N95,G95:N95,"&gt;0")&gt;=1.35,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Model_4_Transmission.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_4_Transmission.xlsx
@@ -3507,10 +3507,25 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="42" t="n"/>
-      <c r="B6" s="42" t="n"/>
-      <c r="C6" s="42" t="n"/>
-      <c r="D6" s="42" t="n"/>
+      <c r="A6" s="42" t="inlineStr">
+        <is>
+          <t>Min DSCR</t>
+        </is>
+      </c>
+      <c r="B6" s="42" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C6" s="42" t="inlineStr">
+        <is>
+          <t>Minimum debt service coverage ratio</t>
+        </is>
+      </c>
+      <c r="D6" s="53">
+        <f>IF(COUNTIF(G95:N95,"&gt;0")&gt;0,MINIFS(G95:N95,G95:N95,"&gt;0"),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="43" t="inlineStr">
@@ -3736,7 +3751,7 @@
         </is>
       </c>
       <c r="D23" s="10">
-        <f>IF(MINIFS(G95:N95,G95:N95,"&gt;0")&gt;=1.35,"PASS","FAIL")</f>
+        <f>IF(D6&gt;=1.35,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
